--- a/ML Progress Sheet - updated.xlsx
+++ b/ML Progress Sheet - updated.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="All AI Features" sheetId="1" state="visible" r:id="rId1"/>
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -109,6 +109,13 @@
       <charset val="1"/>
       <family val="0"/>
       <color rgb="FF9C6500"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
     <font>
@@ -321,7 +328,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -355,9 +362,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -373,8 +377,11 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -382,10 +389,10 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -424,19 +431,19 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -490,6 +497,12 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -499,10 +512,10 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -538,19 +551,19 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1735,12 +1748,12 @@
       </c>
       <c r="C26" s="56" t="inlineStr">
         <is>
-          <t>🔶 Partial</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="D26" s="57" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="E26" s="55" t="inlineStr">
@@ -1750,12 +1763,12 @@
       </c>
       <c r="F26" s="55" t="inlineStr">
         <is>
-          <t>backend/services/mlEngine.js + mlRoutes.js</t>
+          <t>backend/services/mlEngine.js + mlRoutes.js + mlValidationService.js</t>
         </is>
       </c>
       <c r="G26" s="55" t="inlineStr">
         <is>
-          <t>Event-stream EMA + attendance-aware risk bands live. Remaining: accuracy validation on real longitudinal cohorts (not codeable without production data).</t>
+          <t>Event-stream EMA + attendance-aware risk bands live. Retrospective backtest harness (mlValidationService.js + GET /api/ml/class/at-risk-validation) now measures real precision/recall/F1 by predicting at-risk status as of a cutoff and checking each student's own later assessments as ground truth — needs no external data. Remaining: numbers become statistically meaningful once enough longitudinal history accumulates per school (flagged as insufficient_sample below 10 students).</t>
         </is>
       </c>
     </row>
@@ -2501,38 +2514,38 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customFormat="1" customHeight="1" s="53">
-      <c r="A49" s="54" t="inlineStr">
+    <row r="49" ht="15" customFormat="1" customHeight="1" s="47">
+      <c r="A49" s="48" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B49" s="55" t="inlineStr">
+      <c r="B49" s="49" t="inlineStr">
         <is>
           <t>AI Question Paper Generator (teacher selects topic + Bloom)</t>
         </is>
       </c>
-      <c r="C49" s="56" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D49" s="57" t="inlineStr">
+      <c r="C49" s="58" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D49" s="59" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E49" s="55" t="inlineStr">
+      <c r="E49" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F49" s="55" t="inlineStr">
+      <c r="F49" s="49" t="inlineStr">
         <is>
           <t>backend/routes/aiTeacherRoutes.js (quiz-generate) + PracticePaperBuilder.jsx</t>
         </is>
       </c>
-      <c r="G49" s="55" t="inlineStr">
+      <c r="G49" s="49" t="inlineStr">
         <is>
           <t>Backend now accepts a validated bloomLevel param, injects a Bloom-specific instruction into the generation prompt, and passes it to retrieval for bloom-tagged chunk filtering. PracticePaperBuilder.jsx has a teacher-facing Bloom level picker (generation default + per-question override), persisted on PracticePaper.questions[].bloomLevel. Remaining: formal Exam creation (mockExamRoutes.js) still has no AI-generation entry point — only practice papers are wired to the generator.</t>
         </is>
@@ -2984,75 +2997,75 @@
       <c r="F63" s="45" t="n"/>
       <c r="G63" s="46" t="n"/>
     </row>
-    <row r="64" ht="15" customFormat="1" customHeight="1" s="58">
-      <c r="A64" s="59" t="inlineStr">
+    <row r="64" ht="15" customFormat="1" customHeight="1" s="60">
+      <c r="A64" s="61" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="B64" s="60" t="inlineStr">
+      <c r="B64" s="62" t="inlineStr">
         <is>
           <t>Learner Confidence Tracking (dynamic self-perception)</t>
         </is>
       </c>
-      <c r="C64" s="61" t="inlineStr">
+      <c r="C64" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="D64" s="62" t="inlineStr">
+      <c r="D64" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E64" s="60" t="inlineStr">
+      <c r="E64" s="62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F64" s="60" t="inlineStr">
+      <c r="F64" s="62" t="inlineStr">
         <is>
           <t>NEEDED: new model + AI check-in</t>
         </is>
       </c>
-      <c r="G64" s="60" t="inlineStr">
+      <c r="G64" s="62" t="inlineStr">
         <is>
           <t>No model, no UI, no data collection</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customFormat="1" customHeight="1" s="58">
-      <c r="A65" s="59" t="inlineStr">
+    <row r="65" ht="15" customFormat="1" customHeight="1" s="60">
+      <c r="A65" s="61" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="B65" s="60" t="inlineStr">
+      <c r="B65" s="62" t="inlineStr">
         <is>
           <t>Help-Seeking Behaviour (log when/how student asks for help)</t>
         </is>
       </c>
-      <c r="C65" s="61" t="inlineStr">
+      <c r="C65" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="D65" s="62" t="inlineStr">
+      <c r="D65" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E65" s="60" t="inlineStr">
+      <c r="E65" s="62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F65" s="60" t="inlineStr">
+      <c r="F65" s="62" t="inlineStr">
         <is>
           <t>NEEDED: event logging in tutor session</t>
         </is>
       </c>
-      <c r="G65" s="60" t="inlineStr">
+      <c r="G65" s="62" t="inlineStr">
         <is>
           <t>No tracking mechanism</t>
         </is>
@@ -3069,12 +3082,12 @@
           <t>Retention / Forgetting Model (knowledge decay over time)</t>
         </is>
       </c>
-      <c r="C66" s="63" t="inlineStr">
+      <c r="C66" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D66" s="64" t="inlineStr">
+      <c r="D66" s="66" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -3143,12 +3156,12 @@
           <t>Multidimensional Engagement (situational + behavioural + emotional)</t>
         </is>
       </c>
-      <c r="C68" s="63" t="inlineStr">
+      <c r="C68" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D68" s="64" t="inlineStr">
+      <c r="D68" s="66" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -3254,12 +3267,12 @@
           <t>Student Agency (learner control over learning path)</t>
         </is>
       </c>
-      <c r="C71" s="63" t="inlineStr">
+      <c r="C71" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D71" s="64" t="inlineStr">
+      <c r="D71" s="66" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -3291,12 +3304,12 @@
           <t>Explainable AI (why did AI recommend / answer this?)</t>
         </is>
       </c>
-      <c r="C72" s="63" t="inlineStr">
+      <c r="C72" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D72" s="64" t="inlineStr">
+      <c r="D72" s="66" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -3317,38 +3330,38 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="15" customFormat="1" customHeight="1" s="58">
-      <c r="A73" s="59" t="inlineStr">
+    <row r="73" ht="15" customFormat="1" customHeight="1" s="60">
+      <c r="A73" s="61" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="B73" s="60" t="inlineStr">
+      <c r="B73" s="62" t="inlineStr">
         <is>
           <t>Social / Belonging Dimension (peer signals + community)</t>
         </is>
       </c>
-      <c r="C73" s="61" t="inlineStr">
+      <c r="C73" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="D73" s="62" t="inlineStr">
+      <c r="D73" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E73" s="60" t="inlineStr">
+      <c r="E73" s="62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F73" s="60" t="inlineStr">
+      <c r="F73" s="62" t="inlineStr">
         <is>
           <t>Alcove exists for posts; no belonging analytics</t>
         </is>
       </c>
-      <c r="G73" s="60" t="inlineStr">
+      <c r="G73" s="62" t="inlineStr">
         <is>
           <t>No social learning signals</t>
         </is>
@@ -3391,75 +3404,75 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="15" customFormat="1" customHeight="1" s="58">
-      <c r="A75" s="59" t="inlineStr">
+    <row r="75" ht="15" customFormat="1" customHeight="1" s="60">
+      <c r="A75" s="61" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="B75" s="60" t="inlineStr">
+      <c r="B75" s="62" t="inlineStr">
         <is>
           <t>Equity / Bias Monitoring (detect uneven model performance)</t>
         </is>
       </c>
-      <c r="C75" s="61" t="inlineStr">
+      <c r="C75" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="D75" s="62" t="inlineStr">
+      <c r="D75" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E75" s="60" t="inlineStr">
+      <c r="E75" s="62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F75" s="60" t="inlineStr">
+      <c r="F75" s="62" t="inlineStr">
         <is>
           <t>NEEDED: cohort-level analytics overlay</t>
         </is>
       </c>
-      <c r="G75" s="60" t="inlineStr">
+      <c r="G75" s="62" t="inlineStr">
         <is>
           <t>No bias detection</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="15" customFormat="1" customHeight="1" s="58">
-      <c r="A76" s="59" t="inlineStr">
+    <row r="76" ht="15" customFormat="1" customHeight="1" s="60">
+      <c r="A76" s="61" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="B76" s="60" t="inlineStr">
+      <c r="B76" s="62" t="inlineStr">
         <is>
           <t>Wellbeing Safeguards (child protection + human support boundary)</t>
         </is>
       </c>
-      <c r="C76" s="61" t="inlineStr">
+      <c r="C76" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="D76" s="62" t="inlineStr">
+      <c r="D76" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E76" s="60" t="inlineStr">
+      <c r="E76" s="62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F76" s="60" t="inlineStr">
+      <c r="F76" s="62" t="inlineStr">
         <is>
           <t>NEEDED: escalation policy + safeguard layer</t>
         </is>
       </c>
-      <c r="G76" s="60" t="inlineStr">
+      <c r="G76" s="62" t="inlineStr">
         <is>
           <t>Wellbeing CRUD exists; no safeguard framework</t>
         </is>
@@ -3502,8 +3515,8 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="15" customFormat="1" customHeight="1" s="58">
-      <c r="A78" s="65" t="inlineStr">
+    <row r="78" ht="15" customFormat="1" customHeight="1" s="60">
+      <c r="A78" s="67" t="inlineStr">
         <is>
           <t>── 11. FUTURE FEATURES (Architecture doc roadmap) ─────────────────────────────────────────────────────────</t>
         </is>
@@ -3515,38 +3528,38 @@
       <c r="F78" s="45" t="n"/>
       <c r="G78" s="46" t="n"/>
     </row>
-    <row r="79" ht="15" customFormat="1" customHeight="1" s="58">
-      <c r="A79" s="59" t="inlineStr">
+    <row r="79" ht="15" customFormat="1" customHeight="1" s="60">
+      <c r="A79" s="61" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="B79" s="60" t="inlineStr">
+      <c r="B79" s="62" t="inlineStr">
         <is>
           <t>Voice Tutor (speech-to-text + AI response + TTS)</t>
         </is>
       </c>
-      <c r="C79" s="61" t="inlineStr">
+      <c r="C79" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="D79" s="62" t="inlineStr">
+      <c r="D79" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E79" s="60" t="inlineStr">
+      <c r="E79" s="62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F79" s="60" t="inlineStr">
+      <c r="F79" s="62" t="inlineStr">
         <is>
           <t>NEEDED: extend speech module</t>
         </is>
       </c>
-      <c r="G79" s="60" t="inlineStr">
+      <c r="G79" s="62" t="inlineStr">
         <is>
           <t>Speech transcription exists; full voice loop not wired</t>
         </is>
@@ -3589,81 +3602,81 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="15" customFormat="1" customHeight="1" s="58">
-      <c r="A81" s="59" t="inlineStr">
+    <row r="81" ht="15" customFormat="1" customHeight="1" s="60">
+      <c r="A81" s="61" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="B81" s="60" t="inlineStr">
+      <c r="B81" s="62" t="inlineStr">
         <is>
           <t>Video Understanding (lecture video → summary + quiz)</t>
         </is>
       </c>
-      <c r="C81" s="61" t="inlineStr">
+      <c r="C81" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="D81" s="62" t="inlineStr">
+      <c r="D81" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E81" s="60" t="inlineStr">
+      <c r="E81" s="62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F81" s="60" t="inlineStr">
+      <c r="F81" s="62" t="inlineStr">
         <is>
           <t>NEEDED: video ingestion pipeline</t>
         </is>
       </c>
-      <c r="G81" s="60" t="inlineStr">
+      <c r="G81" s="62" t="inlineStr">
         <is>
           <t>No video processing</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="15" customFormat="1" customHeight="1" s="58">
-      <c r="A82" s="59" t="inlineStr">
+    <row r="82" ht="15" customFormat="1" customHeight="1" s="60">
+      <c r="A82" s="61" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="B82" s="60" t="inlineStr">
+      <c r="B82" s="62" t="inlineStr">
         <is>
           <t>Code Tutor (programming support + code review)</t>
         </is>
       </c>
-      <c r="C82" s="61" t="inlineStr">
+      <c r="C82" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="D82" s="62" t="inlineStr">
+      <c r="D82" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E82" s="60" t="inlineStr">
+      <c r="E82" s="62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F82" s="60" t="inlineStr">
+      <c r="F82" s="62" t="inlineStr">
         <is>
           <t>NEEDED: code-specific prompt + execution sandbox</t>
         </is>
       </c>
-      <c r="G82" s="60" t="inlineStr">
+      <c r="G82" s="62" t="inlineStr">
         <is>
           <t>No code tutor mode</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="15" customFormat="1" customHeight="1" s="66">
+    <row r="83" ht="15" customFormat="1" customHeight="1" s="68">
       <c r="A83" s="54" t="inlineStr">
         <is>
           <t>69</t>
@@ -3674,12 +3687,12 @@
           <t>Math Solver (step-by-step equation solving)</t>
         </is>
       </c>
-      <c r="C83" s="63" t="inlineStr">
+      <c r="C83" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D83" s="64" t="inlineStr">
+      <c r="D83" s="66" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -3700,7 +3713,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="15" customFormat="1" customHeight="1" s="66">
+    <row r="84" ht="15" customFormat="1" customHeight="1" s="68">
       <c r="A84" s="54" t="inlineStr">
         <is>
           <t>70</t>
@@ -3711,12 +3724,12 @@
           <t>Topic Failure Prediction (predict fail before test happens)</t>
         </is>
       </c>
-      <c r="C84" s="63" t="inlineStr">
+      <c r="C84" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D84" s="64" t="inlineStr">
+      <c r="D84" s="66" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -3737,44 +3750,44 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="15" customFormat="1" customHeight="1" s="58">
-      <c r="A85" s="59" t="inlineStr">
+    <row r="85" ht="15" customFormat="1" customHeight="1" s="60">
+      <c r="A85" s="61" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B85" s="60" t="inlineStr">
+      <c r="B85" s="62" t="inlineStr">
         <is>
           <t>Learning Style Detection (visual/reading/quiz preference)</t>
         </is>
       </c>
-      <c r="C85" s="61" t="inlineStr">
+      <c r="C85" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="D85" s="62" t="inlineStr">
+      <c r="D85" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E85" s="60" t="inlineStr">
+      <c r="E85" s="62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F85" s="60" t="inlineStr">
+      <c r="F85" s="62" t="inlineStr">
         <is>
           <t>NEEDED: interaction log clustering</t>
         </is>
       </c>
-      <c r="G85" s="60" t="inlineStr">
+      <c r="G85" s="62" t="inlineStr">
         <is>
           <t>No interaction preference tracking</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="15" customFormat="1" customHeight="1" s="66">
+    <row r="86" ht="15" customFormat="1" customHeight="1" s="68">
       <c r="A86" s="54" t="inlineStr">
         <is>
           <t>72</t>
@@ -3785,12 +3798,12 @@
           <t>Performance Forecasting (predicted score on next test)</t>
         </is>
       </c>
-      <c r="C86" s="63" t="inlineStr">
+      <c r="C86" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D86" s="64" t="inlineStr">
+      <c r="D86" s="66" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -3811,7 +3824,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="15" customFormat="1" customHeight="1" s="66">
+    <row r="87" ht="15" customFormat="1" customHeight="1" s="68">
       <c r="A87" s="54" t="inlineStr">
         <is>
           <t>73</t>
@@ -3822,12 +3835,12 @@
           <t>At-risk / Dropout Risk Prediction (ML model)</t>
         </is>
       </c>
-      <c r="C87" s="63" t="inlineStr">
+      <c r="C87" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D87" s="64" t="inlineStr">
+      <c r="D87" s="66" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
@@ -3936,324 +3949,324 @@
       <c r="E4" s="46" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="41">
-      <c r="A5" s="67" t="inlineStr">
+      <c r="A5" s="69" t="inlineStr">
         <is>
           <t>Embedding Engine</t>
         </is>
       </c>
-      <c r="B5" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="C5" s="69" t="inlineStr">
+      <c r="B5" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="C5" s="71" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="D5" s="70" t="inlineStr">
+      <c r="D5" s="72" t="inlineStr">
         <is>
           <t>ai-service/app/modules/embeddings/</t>
         </is>
       </c>
-      <c r="E5" s="70" t="inlineStr">
+      <c r="E5" s="72" t="inlineStr">
         <is>
           <t>Fully wired</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="41">
-      <c r="A6" s="67" t="inlineStr">
+      <c r="A6" s="69" t="inlineStr">
         <is>
           <t>Explain Mode (AI Tutor)</t>
         </is>
       </c>
-      <c r="B6" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="C6" s="69" t="inlineStr">
+      <c r="B6" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="C6" s="71" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="D6" s="70" t="inlineStr">
+      <c r="D6" s="72" t="inlineStr">
         <is>
           <t>ai-service chat module (mode=explain)</t>
         </is>
       </c>
-      <c r="E6" s="70" t="inlineStr">
+      <c r="E6" s="72" t="inlineStr">
         <is>
           <t>Mode works</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="41">
-      <c r="A7" s="67" t="inlineStr">
+      <c r="A7" s="69" t="inlineStr">
         <is>
           <t>ML Engine (EMA mastery)</t>
         </is>
       </c>
-      <c r="B7" s="63" t="inlineStr">
+      <c r="B7" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C7" s="64" t="inlineStr">
+      <c r="C7" s="66" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="D7" s="70" t="inlineStr">
+      <c r="D7" s="72" t="inlineStr">
         <is>
           <t>backend/services/mlEngine.js</t>
         </is>
       </c>
-      <c r="E7" s="70" t="inlineStr">
+      <c r="E7" s="72" t="inlineStr">
         <is>
           <t>Event-stream EMA reader is live; forecast validation remains.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="41">
-      <c r="A8" s="67" t="inlineStr">
+      <c r="A8" s="69" t="inlineStr">
         <is>
           <t>Engagement Scorer</t>
         </is>
       </c>
-      <c r="B8" s="63" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="C8" s="64" t="inlineStr">
+      <c r="B8" s="65" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="C8" s="66" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="D8" s="70" t="inlineStr">
+      <c r="D8" s="72" t="inlineStr">
         <is>
           <t>backend/services/engagementScorer.js</t>
         </is>
       </c>
-      <c r="E8" s="70" t="inlineStr">
+      <c r="E8" s="72" t="inlineStr">
         <is>
           <t>Per-student behavioural + situational + emotional scoring is live; teacher card pending.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="41">
-      <c r="A9" s="67" t="inlineStr">
+      <c r="A9" s="69" t="inlineStr">
         <is>
           <t>Spaced Repetition (SM-2)</t>
         </is>
       </c>
-      <c r="B9" s="63" t="inlineStr">
+      <c r="B9" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C9" s="64" t="inlineStr">
+      <c r="C9" s="66" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="D9" s="70" t="inlineStr">
+      <c r="D9" s="72" t="inlineStr">
         <is>
           <t>backend/models/SpacedRepetitionSchedule.js</t>
         </is>
       </c>
-      <c r="E9" s="70" t="inlineStr">
+      <c r="E9" s="72" t="inlineStr">
         <is>
           <t>SM-2 + cron + recommendation tie-in</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="41">
-      <c r="A10" s="67" t="inlineStr">
+      <c r="A10" s="69" t="inlineStr">
         <is>
           <t>Recommendation Engine</t>
         </is>
       </c>
-      <c r="B10" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="C10" s="69" t="inlineStr">
+      <c r="B10" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="C10" s="71" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="D10" s="70" t="inlineStr">
+      <c r="D10" s="72" t="inlineStr">
         <is>
           <t>backend/routes/recommendationRoutes.js</t>
         </is>
       </c>
-      <c r="E10" s="70" t="inlineStr">
+      <c r="E10" s="72" t="inlineStr">
         <is>
           <t>Engine + acceptance/completion/impact tracking; frontend wiring pending</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="41">
-      <c r="A11" s="67" t="inlineStr">
+      <c r="A11" s="69" t="inlineStr">
         <is>
           <t>At-risk Student Detection</t>
         </is>
       </c>
-      <c r="B11" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="C11" s="69" t="inlineStr">
+      <c r="B11" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="C11" s="71" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="D11" s="70" t="inlineStr">
+      <c r="D11" s="72" t="inlineStr">
         <is>
           <t>backend/routes/mlRoutes.js (GET /class/at-risk)</t>
         </is>
       </c>
-      <c r="E11" s="70" t="inlineStr">
+      <c r="E11" s="72" t="inlineStr">
         <is>
           <t>Scheduled scans + real-time alerts + StudentInsight record</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="41">
-      <c r="A12" s="67" t="inlineStr">
+      <c r="A12" s="69" t="inlineStr">
         <is>
           <t>Engagement Analytics</t>
         </is>
       </c>
-      <c r="B12" s="63" t="inlineStr">
+      <c r="B12" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C12" s="64" t="inlineStr">
+      <c r="C12" s="66" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="D12" s="70" t="inlineStr">
+      <c r="D12" s="72" t="inlineStr">
         <is>
           <t>backend/routes/engagementRoutes.js</t>
         </is>
       </c>
-      <c r="E12" s="70" t="inlineStr">
+      <c r="E12" s="72" t="inlineStr">
         <is>
           <t>Endpoint live; no teacher card</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="41">
-      <c r="A13" s="67" t="inlineStr">
+      <c r="A13" s="69" t="inlineStr">
         <is>
           <t>AI Lesson Content (Teacher)</t>
         </is>
       </c>
-      <c r="B13" s="63" t="inlineStr">
+      <c r="B13" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C13" s="64" t="inlineStr">
+      <c r="C13" s="66" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="D13" s="70" t="inlineStr">
+      <c r="D13" s="72" t="inlineStr">
         <is>
           <t>backend/routes/aiTeacherRoutes.js (lesson-content)</t>
         </is>
       </c>
-      <c r="E13" s="70" t="inlineStr">
+      <c r="E13" s="72" t="inlineStr">
         <is>
           <t>Route + externalised prompt</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="41">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>AI Hinge Question (Teacher)</t>
         </is>
       </c>
-      <c r="B14" s="63" t="inlineStr">
+      <c r="B14" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C14" s="64" t="inlineStr">
+      <c r="C14" s="66" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="D14" s="70" t="inlineStr">
+      <c r="D14" s="72" t="inlineStr">
         <is>
           <t>backend/routes/aiTeacherRoutes.js (hinge-questions)</t>
         </is>
       </c>
-      <c r="E14" s="70" t="inlineStr">
+      <c r="E14" s="72" t="inlineStr">
         <is>
           <t>Route + externalised prompt</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="41">
-      <c r="A15" s="67" t="inlineStr">
+      <c r="A15" s="69" t="inlineStr">
         <is>
           <t>Wellbeing Tracking</t>
         </is>
       </c>
-      <c r="B15" s="63" t="inlineStr">
+      <c r="B15" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C15" s="64" t="inlineStr">
+      <c r="C15" s="66" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="D15" s="70" t="inlineStr">
+      <c r="D15" s="72" t="inlineStr">
         <is>
           <t>backend/models/Wellbeing.js + wellbeingRoute.js</t>
         </is>
       </c>
-      <c r="E15" s="70" t="inlineStr">
+      <c r="E15" s="72" t="inlineStr">
         <is>
           <t>Model + CRUD; no safeguard/escalation layer</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="41">
-      <c r="A16" s="67" t="inlineStr">
+      <c r="A16" s="69" t="inlineStr">
         <is>
           <t>Answer Evaluator (full)</t>
         </is>
       </c>
-      <c r="B16" s="63" t="inlineStr">
+      <c r="B16" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C16" s="64" t="inlineStr">
+      <c r="C16" s="66" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="D16" s="70" t="inlineStr">
+      <c r="D16" s="72" t="inlineStr">
         <is>
           <t>ai-service/app/modules/assessment/</t>
         </is>
       </c>
-      <c r="E16" s="70" t="inlineStr">
+      <c r="E16" s="72" t="inlineStr">
         <is>
           <t>Missing-concept + confidence persisted on exam + assignment + long-answer; needs-review gating</t>
         </is>
@@ -4271,162 +4284,162 @@
       <c r="E17" s="46" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="41">
-      <c r="A18" s="67" t="inlineStr">
+      <c r="A18" s="69" t="inlineStr">
         <is>
           <t>AI Orchestrator</t>
         </is>
       </c>
-      <c r="B18" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="C18" s="69" t="inlineStr">
+      <c r="B18" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="C18" s="71" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="D18" s="70" t="inlineStr">
+      <c r="D18" s="72" t="inlineStr">
         <is>
           <t>NEEDED: ai-service/app/orchestrator/</t>
         </is>
       </c>
-      <c r="E18" s="70" t="inlineStr">
+      <c r="E18" s="72" t="inlineStr">
         <is>
           <t>ai-service/app/modules/orchestrator/ — POST /orchestrate dispatch</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="41">
-      <c r="A19" s="67" t="inlineStr">
+      <c r="A19" s="69" t="inlineStr">
         <is>
           <t>Prompt Library</t>
         </is>
       </c>
-      <c r="B19" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="C19" s="69" t="inlineStr">
+      <c r="B19" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="C19" s="71" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="D19" s="70" t="inlineStr">
+      <c r="D19" s="72" t="inlineStr">
         <is>
           <t>NEEDED: ai-service/prompts/</t>
         </is>
       </c>
-      <c r="E19" s="70" t="inlineStr">
+      <c r="E19" s="72" t="inlineStr">
         <is>
           <t>ai-service/prompts/ + loader.py (~50 files)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="41">
-      <c r="A20" s="67" t="inlineStr">
+      <c r="A20" s="69" t="inlineStr">
         <is>
           <t>Hybrid Search (BM25+vector)</t>
         </is>
       </c>
-      <c r="B20" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="C20" s="69" t="inlineStr">
+      <c r="B20" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="C20" s="71" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="D20" s="70" t="inlineStr">
+      <c r="D20" s="72" t="inlineStr">
         <is>
           <t>NEEDED in retrieval/service.py</t>
         </is>
       </c>
-      <c r="E20" s="70" t="inlineStr">
+      <c r="E20" s="72" t="inlineStr">
         <is>
           <t>RRF fusion of vector + keyword hits in retrieval/service.py</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="41">
-      <c r="A21" s="67" t="inlineStr">
+      <c r="A21" s="69" t="inlineStr">
         <is>
           <t>Document Versioning</t>
         </is>
       </c>
-      <c r="B21" s="63" t="inlineStr">
+      <c r="B21" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C21" s="64" t="inlineStr">
+      <c r="C21" s="66" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="D21" s="70" t="inlineStr">
+      <c r="D21" s="72" t="inlineStr">
         <is>
           <t>NEEDED in TeachingMaterial.js</t>
         </is>
       </c>
-      <c r="E21" s="70" t="inlineStr">
+      <c r="E21" s="72" t="inlineStr">
         <is>
           <t>TeachingMaterial.versions[] + isEnabled; no auto-version-on-reupload / browse UI</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="41">
-      <c r="A22" s="67" t="inlineStr">
+      <c r="A22" s="69" t="inlineStr">
         <is>
           <t>Learning Outcomes Auto-gen</t>
         </is>
       </c>
-      <c r="B22" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="C22" s="69" t="inlineStr">
+      <c r="B22" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="C22" s="71" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="D22" s="70" t="inlineStr">
+      <c r="D22" s="72" t="inlineStr">
         <is>
           <t>NEEDED in documents/service.py</t>
         </is>
       </c>
-      <c r="E22" s="70" t="inlineStr">
+      <c r="E22" s="72" t="inlineStr">
         <is>
           <t>classifier/outcomes on ingest; legacy docs need re-index</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="41">
-      <c r="A23" s="67" t="inlineStr">
+      <c r="A23" s="69" t="inlineStr">
         <is>
           <t>Bloom Engine</t>
         </is>
       </c>
-      <c r="B23" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="C23" s="69" t="inlineStr">
+      <c r="B23" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="C23" s="71" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="D23" s="70" t="inlineStr">
+      <c r="D23" s="72" t="inlineStr">
         <is>
           <t>NEEDED: ai-service/app/modules/bloom/</t>
         </is>
       </c>
-      <c r="E23" s="70" t="inlineStr">
+      <c r="E23" s="72" t="inlineStr">
         <is>
           <t>classifier/bloom on ingest + retrieval filter + question-gen + mastery progression</t>
         </is>
@@ -4444,108 +4457,108 @@
       <c r="E24" s="46" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="41">
-      <c r="A25" s="67" t="inlineStr">
+      <c r="A25" s="69" t="inlineStr">
         <is>
           <t>Worksheet / Homework Gen</t>
         </is>
       </c>
-      <c r="B25" s="63" t="inlineStr">
+      <c r="B25" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C25" s="64" t="inlineStr">
+      <c r="C25" s="66" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D25" s="70" t="inlineStr">
+      <c r="D25" s="72" t="inlineStr">
         <is>
           <t>NEEDED in chat module</t>
         </is>
       </c>
-      <c r="E25" s="70" t="inlineStr">
+      <c r="E25" s="72" t="inlineStr">
         <is>
           <t>POST /api/ai-teacher/worksheet; not personalised to mastery gaps</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="41">
-      <c r="A26" s="67" t="inlineStr">
+      <c r="A26" s="69" t="inlineStr">
         <is>
           <t>Adaptive Difficulty</t>
         </is>
       </c>
-      <c r="B26" s="63" t="inlineStr">
+      <c r="B26" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C26" s="64" t="inlineStr">
+      <c r="C26" s="66" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="D26" s="70" t="inlineStr">
+      <c r="D26" s="72" t="inlineStr">
         <is>
           <t>NEEDED: wire MasteryScore → content generation</t>
         </is>
       </c>
-      <c r="E26" s="70" t="inlineStr">
+      <c r="E26" s="72" t="inlineStr">
         <is>
           <t>Mastery→Bloom band drives difficulty; no full adaptive item selection</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="41">
-      <c r="A27" s="67" t="inlineStr">
+      <c r="A27" s="69" t="inlineStr">
         <is>
           <t>AI Question Paper (Teacher)</t>
         </is>
       </c>
-      <c r="B27" s="63" t="inlineStr">
+      <c r="B27" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C27" s="64" t="inlineStr">
+      <c r="C27" s="66" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="D27" s="70" t="inlineStr">
+      <c r="D27" s="72" t="inlineStr">
         <is>
           <t>NEEDED: Bloom + difficulty param in exam gen</t>
         </is>
       </c>
-      <c r="E27" s="70" t="inlineStr">
+      <c r="E27" s="72" t="inlineStr">
         <is>
           <t>Bloom-level question gen exists; teacher selection UI pending</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="41">
-      <c r="A28" s="67" t="inlineStr">
+      <c r="A28" s="69" t="inlineStr">
         <is>
           <t>Teacher AI Override</t>
         </is>
       </c>
-      <c r="B28" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="C28" s="69" t="inlineStr">
+      <c r="B28" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="C28" s="71" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="D28" s="70" t="inlineStr">
+      <c r="D28" s="72" t="inlineStr">
         <is>
           <t>NEEDED: annotation layer on AI responses</t>
         </is>
       </c>
-      <c r="E28" s="70" t="inlineStr">
+      <c r="E28" s="72" t="inlineStr">
         <is>
           <t>correct-answer + withdraw + list endpoints; audited + allocation-scoped; frontend pending</t>
         </is>
@@ -4563,351 +4576,351 @@
       <c r="E29" s="46" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="41">
-      <c r="A30" s="67" t="inlineStr">
+      <c r="A30" s="69" t="inlineStr">
         <is>
           <t>Learner Confidence</t>
         </is>
       </c>
-      <c r="B30" s="61" t="inlineStr">
+      <c r="B30" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="C30" s="62" t="inlineStr">
+      <c r="C30" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D30" s="70" t="inlineStr">
+      <c r="D30" s="72" t="inlineStr">
         <is>
           <t>NEEDED: new model + AI check-in flow</t>
         </is>
       </c>
-      <c r="E30" s="70" t="inlineStr">
+      <c r="E30" s="72" t="inlineStr">
         <is>
           <t>No data collection</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="41">
-      <c r="A31" s="67" t="inlineStr">
+      <c r="A31" s="69" t="inlineStr">
         <is>
           <t>Help-Seeking Behaviour</t>
         </is>
       </c>
-      <c r="B31" s="61" t="inlineStr">
+      <c r="B31" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="C31" s="62" t="inlineStr">
+      <c r="C31" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D31" s="70" t="inlineStr">
+      <c r="D31" s="72" t="inlineStr">
         <is>
           <t>NEEDED: event logging in tutor session</t>
         </is>
       </c>
-      <c r="E31" s="70" t="inlineStr">
+      <c r="E31" s="72" t="inlineStr">
         <is>
           <t>No tracking</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="41">
-      <c r="A32" s="67" t="inlineStr">
+      <c r="A32" s="69" t="inlineStr">
         <is>
           <t>Misconceptions Engine</t>
         </is>
       </c>
-      <c r="B32" s="63" t="inlineStr">
+      <c r="B32" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C32" s="64" t="inlineStr">
+      <c r="C32" s="66" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="D32" s="70" t="inlineStr">
+      <c r="D32" s="72" t="inlineStr">
         <is>
           <t>NEEDED: extend error classifier</t>
         </is>
       </c>
-      <c r="E32" s="70" t="inlineStr">
+      <c r="E32" s="72" t="inlineStr">
         <is>
           <t>Class-wide aggregation + tutor mode; per-student model pending</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="41">
-      <c r="A33" s="67" t="inlineStr">
+      <c r="A33" s="69" t="inlineStr">
         <is>
           <t>Multidimensional Engagement</t>
         </is>
       </c>
-      <c r="B33" s="63" t="inlineStr">
+      <c r="B33" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C33" s="64" t="inlineStr">
+      <c r="C33" s="66" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D33" s="70" t="inlineStr">
+      <c r="D33" s="72" t="inlineStr">
         <is>
           <t>engagementScorer.js (behavioural only)</t>
         </is>
       </c>
-      <c r="E33" s="70" t="inlineStr">
+      <c r="E33" s="72" t="inlineStr">
         <is>
           <t>Situational + emotional dimensions missing</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="41">
-      <c r="A34" s="67" t="inlineStr">
+      <c r="A34" s="69" t="inlineStr">
         <is>
           <t>Intervention Effectiveness</t>
         </is>
       </c>
-      <c r="B34" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="C34" s="69" t="inlineStr">
+      <c r="B34" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="C34" s="71" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="D34" s="70" t="inlineStr">
+      <c r="D34" s="72" t="inlineStr">
         <is>
           <t>NEEDED: analytics on interventions</t>
         </is>
       </c>
-      <c r="E34" s="70" t="inlineStr">
+      <c r="E34" s="72" t="inlineStr">
         <is>
           <t>Auto follow-up + 7/14/30-day checkpoints + automatic improvement calc + auto-finalize</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="41">
-      <c r="A35" s="67" t="inlineStr">
+      <c r="A35" s="69" t="inlineStr">
         <is>
           <t>Teacher Escalation</t>
         </is>
       </c>
-      <c r="B35" s="63" t="inlineStr">
+      <c r="B35" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C35" s="64" t="inlineStr">
+      <c r="C35" s="66" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="D35" s="70" t="inlineStr">
+      <c r="D35" s="72" t="inlineStr">
         <is>
           <t>NEEDED: alert from gap/at-risk engine</t>
         </is>
       </c>
-      <c r="E35" s="70" t="inlineStr">
+      <c r="E35" s="72" t="inlineStr">
         <is>
           <t>Auto intervention-plan creation on alert; counsellor/leadership escalation not built</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="41">
-      <c r="A36" s="67" t="inlineStr">
+      <c r="A36" s="69" t="inlineStr">
         <is>
           <t>Student Agency</t>
         </is>
       </c>
-      <c r="B36" s="63" t="inlineStr">
+      <c r="B36" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C36" s="64" t="inlineStr">
+      <c r="C36" s="66" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="D36" s="70" t="inlineStr">
+      <c r="D36" s="72" t="inlineStr">
         <is>
           <t>NEEDED: path selection UI</t>
         </is>
       </c>
-      <c r="E36" s="70" t="inlineStr">
+      <c r="E36" s="72" t="inlineStr">
         <is>
           <t>Accept/dismiss/complete recommendations; no path-selection UI</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="41">
-      <c r="A37" s="67" t="inlineStr">
+      <c r="A37" s="69" t="inlineStr">
         <is>
           <t>Explainable AI</t>
         </is>
       </c>
-      <c r="B37" s="63" t="inlineStr">
+      <c r="B37" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C37" s="64" t="inlineStr">
+      <c r="C37" s="66" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D37" s="70" t="inlineStr">
+      <c r="D37" s="72" t="inlineStr">
         <is>
           <t>NEEDED: reasoning trace in tutor response</t>
         </is>
       </c>
-      <c r="E37" s="70" t="inlineStr">
+      <c r="E37" s="72" t="inlineStr">
         <is>
           <t>Explainability string on recs; no reasoning-trace/lineage logging</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="41">
-      <c r="A38" s="67" t="inlineStr">
+      <c r="A38" s="69" t="inlineStr">
         <is>
           <t>Social / Belonging</t>
         </is>
       </c>
-      <c r="B38" s="61" t="inlineStr">
+      <c r="B38" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="C38" s="62" t="inlineStr">
+      <c r="C38" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D38" s="70" t="inlineStr">
+      <c r="D38" s="72" t="inlineStr">
         <is>
           <t>Alcove posts exist; no belonging analytics</t>
         </is>
       </c>
-      <c r="E38" s="70" t="inlineStr">
+      <c r="E38" s="72" t="inlineStr">
         <is>
           <t>No social learning signals</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="41">
-      <c r="A39" s="67" t="inlineStr">
+      <c r="A39" s="69" t="inlineStr">
         <is>
           <t>Evidence Testing</t>
         </is>
       </c>
-      <c r="B39" s="63" t="inlineStr">
+      <c r="B39" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C39" s="64" t="inlineStr">
+      <c r="C39" s="66" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D39" s="70" t="inlineStr">
+      <c r="D39" s="72" t="inlineStr">
         <is>
           <t>NEEDED: pre/post outcome measurement</t>
         </is>
       </c>
-      <c r="E39" s="70" t="inlineStr">
+      <c r="E39" s="72" t="inlineStr">
         <is>
           <t>Evidence summaries + forecast infra; no pre/post framework</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="41">
-      <c r="A40" s="67" t="inlineStr">
+      <c r="A40" s="69" t="inlineStr">
         <is>
           <t>Equity / Bias Monitoring</t>
         </is>
       </c>
-      <c r="B40" s="61" t="inlineStr">
+      <c r="B40" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="C40" s="62" t="inlineStr">
+      <c r="C40" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D40" s="70" t="inlineStr">
+      <c r="D40" s="72" t="inlineStr">
         <is>
           <t>NEEDED: cohort analytics overlay</t>
         </is>
       </c>
-      <c r="E40" s="70" t="inlineStr">
+      <c r="E40" s="72" t="inlineStr">
         <is>
           <t>No bias detection</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="41">
-      <c r="A41" s="67" t="inlineStr">
+      <c r="A41" s="69" t="inlineStr">
         <is>
           <t>Wellbeing Safeguards</t>
         </is>
       </c>
-      <c r="B41" s="61" t="inlineStr">
+      <c r="B41" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="C41" s="62" t="inlineStr">
+      <c r="C41" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D41" s="70" t="inlineStr">
+      <c r="D41" s="72" t="inlineStr">
         <is>
           <t>NEEDED: escalation policy + child protection</t>
         </is>
       </c>
-      <c r="E41" s="70" t="inlineStr">
+      <c r="E41" s="72" t="inlineStr">
         <is>
           <t>Wellbeing CRUD exists; no safeguard layer</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="41">
-      <c r="A42" s="67" t="inlineStr">
+      <c r="A42" s="69" t="inlineStr">
         <is>
           <t>AI / Data Ethics Framework</t>
         </is>
       </c>
-      <c r="B42" s="63" t="inlineStr">
+      <c r="B42" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C42" s="64" t="inlineStr">
+      <c r="C42" s="66" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="D42" s="70" t="inlineStr">
+      <c r="D42" s="72" t="inlineStr">
         <is>
           <t>JWT + RBAC + tenant isolation done</t>
         </is>
       </c>
-      <c r="E42" s="70" t="inlineStr">
+      <c r="E42" s="72" t="inlineStr">
         <is>
           <t>RBAC + tenant isolation; no child-ethics/consent framework</t>
         </is>
@@ -4925,189 +4938,189 @@
       <c r="E43" s="46" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="41">
-      <c r="A44" s="67" t="inlineStr">
+      <c r="A44" s="69" t="inlineStr">
         <is>
           <t>Voice Tutor</t>
         </is>
       </c>
-      <c r="B44" s="61" t="inlineStr">
+      <c r="B44" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="C44" s="62" t="inlineStr">
+      <c r="C44" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D44" s="70" t="inlineStr">
+      <c r="D44" s="72" t="inlineStr">
         <is>
           <t>Extend speech module</t>
         </is>
       </c>
-      <c r="E44" s="70" t="inlineStr">
+      <c r="E44" s="72" t="inlineStr">
         <is>
           <t>Transcription exists; full voice loop not wired</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="41">
-      <c r="A45" s="67" t="inlineStr">
+      <c r="A45" s="69" t="inlineStr">
         <is>
           <t>Image Understanding</t>
         </is>
       </c>
-      <c r="B45" s="63" t="inlineStr">
+      <c r="B45" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C45" s="64" t="inlineStr">
+      <c r="C45" s="66" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D45" s="70" t="inlineStr">
+      <c r="D45" s="72" t="inlineStr">
         <is>
           <t>NEEDED: vision model (LLaVA/Qwen-VL)</t>
         </is>
       </c>
-      <c r="E45" s="70" t="inlineStr">
+      <c r="E45" s="72" t="inlineStr">
         <is>
           <t>vision module + explain-image + PDF-page vision + visual_explain mode; student upload flow pending</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="41">
-      <c r="A46" s="67" t="inlineStr">
+      <c r="A46" s="69" t="inlineStr">
         <is>
           <t>Video Understanding</t>
         </is>
       </c>
-      <c r="B46" s="61" t="inlineStr">
+      <c r="B46" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="C46" s="62" t="inlineStr">
+      <c r="C46" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D46" s="70" t="inlineStr">
+      <c r="D46" s="72" t="inlineStr">
         <is>
           <t>NEEDED: video ingestion pipeline</t>
         </is>
       </c>
-      <c r="E46" s="70" t="inlineStr">
+      <c r="E46" s="72" t="inlineStr">
         <is>
           <t>No video processing</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="41">
-      <c r="A47" s="67" t="inlineStr">
+      <c r="A47" s="69" t="inlineStr">
         <is>
           <t>Code Tutor</t>
         </is>
       </c>
-      <c r="B47" s="61" t="inlineStr">
+      <c r="B47" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="C47" s="62" t="inlineStr">
+      <c r="C47" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D47" s="70" t="inlineStr">
+      <c r="D47" s="72" t="inlineStr">
         <is>
           <t>NEEDED: code-mode prompt + sandbox</t>
         </is>
       </c>
-      <c r="E47" s="70" t="inlineStr">
+      <c r="E47" s="72" t="inlineStr">
         <is>
           <t>No code tutor mode</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="41">
-      <c r="A48" s="67" t="inlineStr">
+      <c r="A48" s="69" t="inlineStr">
         <is>
           <t>Math Solver</t>
         </is>
       </c>
-      <c r="B48" s="63" t="inlineStr">
+      <c r="B48" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C48" s="64" t="inlineStr">
+      <c r="C48" s="66" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="D48" s="70" t="inlineStr">
+      <c r="D48" s="72" t="inlineStr">
         <is>
           <t>NEEDED: math model (Qwen-Math)</t>
         </is>
       </c>
-      <c r="E48" s="70" t="inlineStr">
+      <c r="E48" s="72" t="inlineStr">
         <is>
           <t>stem/verifier.py math-answer verification; step-by-step UI + math model pending</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="41">
-      <c r="A49" s="67" t="inlineStr">
+      <c r="A49" s="69" t="inlineStr">
         <is>
           <t>Topic Failure Prediction</t>
         </is>
       </c>
-      <c r="B49" s="63" t="inlineStr">
+      <c r="B49" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="C49" s="64" t="inlineStr">
+      <c r="C49" s="66" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D49" s="70" t="inlineStr">
+      <c r="D49" s="72" t="inlineStr">
         <is>
           <t>NEEDED: time-series over mastery decay</t>
         </is>
       </c>
-      <c r="E49" s="70" t="inlineStr">
+      <c r="E49" s="72" t="inlineStr">
         <is>
           <t>forecastScores infra; unvalidated, not surfaced</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="41">
-      <c r="A50" s="67" t="inlineStr">
+      <c r="A50" s="69" t="inlineStr">
         <is>
           <t>Learning Style Detection</t>
         </is>
       </c>
-      <c r="B50" s="61" t="inlineStr">
+      <c r="B50" s="63" t="inlineStr">
         <is>
           <t>❌ Not Started</t>
         </is>
       </c>
-      <c r="C50" s="62" t="inlineStr">
+      <c r="C50" s="64" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D50" s="70" t="inlineStr">
+      <c r="D50" s="72" t="inlineStr">
         <is>
           <t>NEEDED: interaction log clustering</t>
         </is>
       </c>
-      <c r="E50" s="70" t="inlineStr">
+      <c r="E50" s="72" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
@@ -5200,224 +5213,224 @@
       <c r="F4" s="46" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="41">
-      <c r="A5" s="67" t="inlineStr">
+      <c r="A5" s="69" t="inlineStr">
         <is>
           <t>Admin.js</t>
         </is>
       </c>
-      <c r="B5" s="70" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>Admin user schema</t>
         </is>
       </c>
-      <c r="C5" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D5" s="69" t="inlineStr">
+      <c r="C5" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D5" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E5" s="70" t="inlineStr">
+      <c r="E5" s="72" t="inlineStr">
         <is>
           <t>adminRoutes.js</t>
         </is>
       </c>
-      <c r="F5" s="70" t="inlineStr">
+      <c r="F5" s="72" t="inlineStr">
         <is>
           <t>Full CRUD + RBAC</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="41">
-      <c r="A6" s="67" t="inlineStr">
+      <c r="A6" s="69" t="inlineStr">
         <is>
           <t>ParentUser.js</t>
         </is>
       </c>
-      <c r="B6" s="70" t="inlineStr">
+      <c r="B6" s="72" t="inlineStr">
         <is>
           <t>Parent account</t>
         </is>
       </c>
-      <c r="C6" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D6" s="69" t="inlineStr">
+      <c r="C6" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D6" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E6" s="70" t="inlineStr">
+      <c r="E6" s="72" t="inlineStr">
         <is>
           <t>parentRoute.js</t>
         </is>
       </c>
-      <c r="F6" s="70" t="inlineStr">
+      <c r="F6" s="72" t="inlineStr">
         <is>
           <t>Full portal</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="41">
-      <c r="A7" s="67" t="inlineStr">
+      <c r="A7" s="69" t="inlineStr">
         <is>
           <t>Principal.js</t>
         </is>
       </c>
-      <c r="B7" s="70" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>Principal account</t>
         </is>
       </c>
-      <c r="C7" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D7" s="69" t="inlineStr">
+      <c r="C7" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D7" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E7" s="70" t="inlineStr">
+      <c r="E7" s="72" t="inlineStr">
         <is>
           <t>principalRoutes.js</t>
         </is>
       </c>
-      <c r="F7" s="70" t="inlineStr">
+      <c r="F7" s="72" t="inlineStr">
         <is>
           <t>Full portal</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="41">
-      <c r="A8" s="67" t="inlineStr">
+      <c r="A8" s="69" t="inlineStr">
         <is>
           <t>StaffUser.js</t>
         </is>
       </c>
-      <c r="B8" s="70" t="inlineStr">
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>Non-teaching staff</t>
         </is>
       </c>
-      <c r="C8" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D8" s="69" t="inlineStr">
+      <c r="C8" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D8" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E8" s="70" t="inlineStr">
+      <c r="E8" s="72" t="inlineStr">
         <is>
           <t>staffRoutes.js</t>
         </is>
       </c>
-      <c r="F8" s="70" t="inlineStr">
+      <c r="F8" s="72" t="inlineStr">
         <is>
           <t>Full portal</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="41">
-      <c r="A9" s="67" t="inlineStr">
+      <c r="A9" s="69" t="inlineStr">
         <is>
           <t>StudentUser.js</t>
         </is>
       </c>
-      <c r="B9" s="70" t="inlineStr">
+      <c r="B9" s="72" t="inlineStr">
         <is>
           <t>Student account</t>
         </is>
       </c>
-      <c r="C9" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D9" s="69" t="inlineStr">
+      <c r="C9" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D9" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E9" s="70" t="inlineStr">
+      <c r="E9" s="72" t="inlineStr">
         <is>
           <t>studentRoute.js</t>
         </is>
       </c>
-      <c r="F9" s="70" t="inlineStr">
+      <c r="F9" s="72" t="inlineStr">
         <is>
           <t>Full portal</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="41">
-      <c r="A10" s="67" t="inlineStr">
+      <c r="A10" s="69" t="inlineStr">
         <is>
           <t>TeacherUser.js</t>
         </is>
       </c>
-      <c r="B10" s="70" t="inlineStr">
+      <c r="B10" s="72" t="inlineStr">
         <is>
           <t>Teacher account</t>
         </is>
       </c>
-      <c r="C10" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D10" s="69" t="inlineStr">
+      <c r="C10" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D10" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E10" s="70" t="inlineStr">
+      <c r="E10" s="72" t="inlineStr">
         <is>
           <t>teacherRoute.js</t>
         </is>
       </c>
-      <c r="F10" s="70" t="inlineStr">
+      <c r="F10" s="72" t="inlineStr">
         <is>
           <t>Full portal</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="41">
-      <c r="A11" s="67" t="inlineStr">
+      <c r="A11" s="69" t="inlineStr">
         <is>
           <t>SuperAdminActivity.js</t>
         </is>
       </c>
-      <c r="B11" s="70" t="inlineStr">
+      <c r="B11" s="72" t="inlineStr">
         <is>
           <t>Super-admin audit log</t>
         </is>
       </c>
-      <c r="C11" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D11" s="69" t="inlineStr">
+      <c r="C11" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D11" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E11" s="70" t="inlineStr">
+      <c r="E11" s="72" t="inlineStr">
         <is>
           <t>superAdminRoutes.js</t>
         </is>
       </c>
-      <c r="F11" s="70" t="inlineStr">
+      <c r="F11" s="72" t="inlineStr">
         <is>
           <t>Audit trail</t>
         </is>
@@ -5436,416 +5449,416 @@
       <c r="F12" s="46" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="41">
-      <c r="A13" s="67" t="inlineStr">
+      <c r="A13" s="69" t="inlineStr">
         <is>
           <t>Organization.js</t>
         </is>
       </c>
-      <c r="B13" s="70" t="inlineStr">
+      <c r="B13" s="72" t="inlineStr">
         <is>
           <t>Top-level tenant</t>
         </is>
       </c>
-      <c r="C13" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D13" s="69" t="inlineStr">
+      <c r="C13" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D13" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E13" s="70" t="inlineStr">
+      <c r="E13" s="72" t="inlineStr">
         <is>
           <t>organizationRoutes.js</t>
         </is>
       </c>
-      <c r="F13" s="70" t="inlineStr">
+      <c r="F13" s="72" t="inlineStr">
         <is>
           <t>Multi-tenant root</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="41">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>School.js</t>
         </is>
       </c>
-      <c r="B14" s="70" t="inlineStr">
+      <c r="B14" s="72" t="inlineStr">
         <is>
           <t>School entity</t>
         </is>
       </c>
-      <c r="C14" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D14" s="69" t="inlineStr">
+      <c r="C14" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D14" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E14" s="70" t="inlineStr">
+      <c r="E14" s="72" t="inlineStr">
         <is>
           <t>schoolRoutes.js</t>
         </is>
       </c>
-      <c r="F14" s="70" t="inlineStr">
+      <c r="F14" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="41">
-      <c r="A15" s="67" t="inlineStr">
+      <c r="A15" s="69" t="inlineStr">
         <is>
           <t>AcademicYear.js</t>
         </is>
       </c>
-      <c r="B15" s="70" t="inlineStr">
+      <c r="B15" s="72" t="inlineStr">
         <is>
           <t>Academic year</t>
         </is>
       </c>
-      <c r="C15" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D15" s="69" t="inlineStr">
+      <c r="C15" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D15" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E15" s="70" t="inlineStr">
+      <c r="E15" s="72" t="inlineStr">
         <is>
           <t>academicRoutes.js</t>
         </is>
       </c>
-      <c r="F15" s="70" t="inlineStr">
+      <c r="F15" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="41">
-      <c r="A16" s="67" t="inlineStr">
+      <c r="A16" s="69" t="inlineStr">
         <is>
           <t>Class.js</t>
         </is>
       </c>
-      <c r="B16" s="70" t="inlineStr">
+      <c r="B16" s="72" t="inlineStr">
         <is>
           <t>Class / grade</t>
         </is>
       </c>
-      <c r="C16" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D16" s="69" t="inlineStr">
+      <c r="C16" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D16" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E16" s="70" t="inlineStr">
+      <c r="E16" s="72" t="inlineStr">
         <is>
           <t>academicRoutes.js</t>
         </is>
       </c>
-      <c r="F16" s="70" t="inlineStr">
+      <c r="F16" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="41">
-      <c r="A17" s="67" t="inlineStr">
+      <c r="A17" s="69" t="inlineStr">
         <is>
           <t>Section.js</t>
         </is>
       </c>
-      <c r="B17" s="70" t="inlineStr">
+      <c r="B17" s="72" t="inlineStr">
         <is>
           <t>Section in class</t>
         </is>
       </c>
-      <c r="C17" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D17" s="69" t="inlineStr">
+      <c r="C17" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D17" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E17" s="70" t="inlineStr">
+      <c r="E17" s="72" t="inlineStr">
         <is>
           <t>academicRoutes.js</t>
         </is>
       </c>
-      <c r="F17" s="70" t="inlineStr">
+      <c r="F17" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="41">
-      <c r="A18" s="67" t="inlineStr">
+      <c r="A18" s="69" t="inlineStr">
         <is>
           <t>Subject.js</t>
         </is>
       </c>
-      <c r="B18" s="70" t="inlineStr">
+      <c r="B18" s="72" t="inlineStr">
         <is>
           <t>Subject entity</t>
         </is>
       </c>
-      <c r="C18" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D18" s="69" t="inlineStr">
+      <c r="C18" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D18" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E18" s="70" t="inlineStr">
+      <c r="E18" s="72" t="inlineStr">
         <is>
           <t>subjectRoute.js</t>
         </is>
       </c>
-      <c r="F18" s="70" t="inlineStr">
+      <c r="F18" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="41">
-      <c r="A19" s="67" t="inlineStr">
+      <c r="A19" s="69" t="inlineStr">
         <is>
           <t>Department.js</t>
         </is>
       </c>
-      <c r="B19" s="70" t="inlineStr">
+      <c r="B19" s="72" t="inlineStr">
         <is>
           <t>Teacher department</t>
         </is>
       </c>
-      <c r="C19" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D19" s="69" t="inlineStr">
+      <c r="C19" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D19" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E19" s="70" t="inlineStr">
+      <c r="E19" s="72" t="inlineStr">
         <is>
           <t>departmentRoutes.js</t>
         </is>
       </c>
-      <c r="F19" s="70" t="inlineStr">
+      <c r="F19" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="41">
-      <c r="A20" s="67" t="inlineStr">
+      <c r="A20" s="69" t="inlineStr">
         <is>
           <t>Timetable.js</t>
         </is>
       </c>
-      <c r="B20" s="70" t="inlineStr">
+      <c r="B20" s="72" t="inlineStr">
         <is>
           <t>Class timetable</t>
         </is>
       </c>
-      <c r="C20" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D20" s="69" t="inlineStr">
+      <c r="C20" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D20" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E20" s="70" t="inlineStr">
+      <c r="E20" s="72" t="inlineStr">
         <is>
           <t>timetableRoutes.js</t>
         </is>
       </c>
-      <c r="F20" s="70" t="inlineStr">
+      <c r="F20" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="41">
-      <c r="A21" s="67" t="inlineStr">
+      <c r="A21" s="69" t="inlineStr">
         <is>
           <t>Building.js</t>
         </is>
       </c>
-      <c r="B21" s="70" t="inlineStr">
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>Campus building</t>
         </is>
       </c>
-      <c r="C21" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D21" s="69" t="inlineStr">
+      <c r="C21" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D21" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E21" s="70" t="inlineStr">
+      <c r="E21" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="70" t="inlineStr">
+      <c r="F21" s="72" t="inlineStr">
         <is>
           <t>Reference data</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="41">
-      <c r="A22" s="67" t="inlineStr">
+      <c r="A22" s="69" t="inlineStr">
         <is>
           <t>Floor.js</t>
         </is>
       </c>
-      <c r="B22" s="70" t="inlineStr">
+      <c r="B22" s="72" t="inlineStr">
         <is>
           <t>Floor in building</t>
         </is>
       </c>
-      <c r="C22" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D22" s="69" t="inlineStr">
+      <c r="C22" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D22" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E22" s="70" t="inlineStr">
+      <c r="E22" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="70" t="inlineStr">
+      <c r="F22" s="72" t="inlineStr">
         <is>
           <t>Reference data</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="41">
-      <c r="A23" s="67" t="inlineStr">
+      <c r="A23" s="69" t="inlineStr">
         <is>
           <t>Room.js</t>
         </is>
       </c>
-      <c r="B23" s="70" t="inlineStr">
+      <c r="B23" s="72" t="inlineStr">
         <is>
           <t>Classroom entity</t>
         </is>
       </c>
-      <c r="C23" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D23" s="69" t="inlineStr">
+      <c r="C23" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D23" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E23" s="70" t="inlineStr">
+      <c r="E23" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F23" s="70" t="inlineStr">
+      <c r="F23" s="72" t="inlineStr">
         <is>
           <t>Reference data</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="41">
-      <c r="A24" s="67" t="inlineStr">
+      <c r="A24" s="69" t="inlineStr">
         <is>
           <t>Holiday.js</t>
         </is>
       </c>
-      <c r="B24" s="70" t="inlineStr">
+      <c r="B24" s="72" t="inlineStr">
         <is>
           <t>Holiday calendar</t>
         </is>
       </c>
-      <c r="C24" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D24" s="69" t="inlineStr">
+      <c r="C24" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D24" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E24" s="70" t="inlineStr">
+      <c r="E24" s="72" t="inlineStr">
         <is>
           <t>holidayRoutes.js</t>
         </is>
       </c>
-      <c r="F24" s="70" t="inlineStr">
+      <c r="F24" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="41">
-      <c r="A25" s="67" t="inlineStr">
+      <c r="A25" s="69" t="inlineStr">
         <is>
           <t>TeacherAllocation.js</t>
         </is>
       </c>
-      <c r="B25" s="70" t="inlineStr">
+      <c r="B25" s="72" t="inlineStr">
         <is>
           <t>Teacher → class-subject</t>
         </is>
       </c>
-      <c r="C25" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D25" s="69" t="inlineStr">
+      <c r="C25" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D25" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E25" s="70" t="inlineStr">
+      <c r="E25" s="72" t="inlineStr">
         <is>
           <t>teacherAllocationRoutes.js</t>
         </is>
       </c>
-      <c r="F25" s="70" t="inlineStr">
+      <c r="F25" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
@@ -5864,384 +5877,384 @@
       <c r="F26" s="46" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="41">
-      <c r="A27" s="67" t="inlineStr">
+      <c r="A27" s="69" t="inlineStr">
         <is>
           <t>Assignment.js</t>
         </is>
       </c>
-      <c r="B27" s="70" t="inlineStr">
+      <c r="B27" s="72" t="inlineStr">
         <is>
           <t>Assignment + submissions</t>
         </is>
       </c>
-      <c r="C27" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D27" s="69" t="inlineStr">
+      <c r="C27" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D27" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E27" s="70" t="inlineStr">
+      <c r="E27" s="72" t="inlineStr">
         <is>
           <t>assignmentRoute.js</t>
         </is>
       </c>
-      <c r="F27" s="70" t="inlineStr">
+      <c r="F27" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="41">
-      <c r="A28" s="67" t="inlineStr">
+      <c r="A28" s="69" t="inlineStr">
         <is>
           <t>Exam.js</t>
         </is>
       </c>
-      <c r="B28" s="70" t="inlineStr">
+      <c r="B28" s="72" t="inlineStr">
         <is>
           <t>Exam entity</t>
         </is>
       </c>
-      <c r="C28" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D28" s="69" t="inlineStr">
+      <c r="C28" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D28" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E28" s="70" t="inlineStr">
+      <c r="E28" s="72" t="inlineStr">
         <is>
           <t>examRoute.js</t>
         </is>
       </c>
-      <c r="F28" s="70" t="inlineStr">
+      <c r="F28" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="41">
-      <c r="A29" s="67" t="inlineStr">
+      <c r="A29" s="69" t="inlineStr">
         <is>
           <t>ExamAttempt.js</t>
         </is>
       </c>
-      <c r="B29" s="70" t="inlineStr">
+      <c r="B29" s="72" t="inlineStr">
         <is>
           <t>Student exam attempt</t>
         </is>
       </c>
-      <c r="C29" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D29" s="69" t="inlineStr">
+      <c r="C29" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D29" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E29" s="70" t="inlineStr">
+      <c r="E29" s="72" t="inlineStr">
         <is>
           <t>examRoute.js</t>
         </is>
       </c>
-      <c r="F29" s="70" t="inlineStr">
+      <c r="F29" s="72" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="41">
-      <c r="A30" s="67" t="inlineStr">
+      <c r="A30" s="69" t="inlineStr">
         <is>
           <t>ExamGroup.js</t>
         </is>
       </c>
-      <c r="B30" s="70" t="inlineStr">
+      <c r="B30" s="72" t="inlineStr">
         <is>
           <t>Exam grouping</t>
         </is>
       </c>
-      <c r="C30" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D30" s="69" t="inlineStr">
+      <c r="C30" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D30" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E30" s="70" t="inlineStr">
+      <c r="E30" s="72" t="inlineStr">
         <is>
           <t>examRoute.js</t>
         </is>
       </c>
-      <c r="F30" s="70" t="inlineStr">
+      <c r="F30" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="41">
-      <c r="A31" s="67" t="inlineStr">
+      <c r="A31" s="69" t="inlineStr">
         <is>
           <t>ExamQuestion.js</t>
         </is>
       </c>
-      <c r="B31" s="70" t="inlineStr">
+      <c r="B31" s="72" t="inlineStr">
         <is>
           <t>MCQ/short/long question</t>
         </is>
       </c>
-      <c r="C31" s="63" t="inlineStr">
+      <c r="C31" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D31" s="64" t="inlineStr">
+      <c r="D31" s="66" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="E31" s="70" t="inlineStr">
+      <c r="E31" s="72" t="inlineStr">
         <is>
           <t>examRoute.js</t>
         </is>
       </c>
-      <c r="F31" s="70" t="inlineStr">
+      <c r="F31" s="72" t="inlineStr">
         <is>
           <t>Evaluator wired for written answers; no Bloom/difficulty calibration</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="41">
-      <c r="A32" s="67" t="inlineStr">
+      <c r="A32" s="69" t="inlineStr">
         <is>
           <t>ExamResult.js</t>
         </is>
       </c>
-      <c r="B32" s="70" t="inlineStr">
+      <c r="B32" s="72" t="inlineStr">
         <is>
           <t>Exam result record</t>
         </is>
       </c>
-      <c r="C32" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D32" s="69" t="inlineStr">
+      <c r="C32" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D32" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E32" s="70" t="inlineStr">
+      <c r="E32" s="72" t="inlineStr">
         <is>
           <t>examRoute.js</t>
         </is>
       </c>
-      <c r="F32" s="70" t="inlineStr">
+      <c r="F32" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="41">
-      <c r="A33" s="67" t="inlineStr">
+      <c r="A33" s="69" t="inlineStr">
         <is>
           <t>LessonPlan.js</t>
         </is>
       </c>
-      <c r="B33" s="70" t="inlineStr">
+      <c r="B33" s="72" t="inlineStr">
         <is>
           <t>Teacher lesson plan</t>
         </is>
       </c>
-      <c r="C33" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D33" s="69" t="inlineStr">
+      <c r="C33" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D33" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E33" s="70" t="inlineStr">
+      <c r="E33" s="72" t="inlineStr">
         <is>
           <t>lessonPlanRoutes.js</t>
         </is>
       </c>
-      <c r="F33" s="70" t="inlineStr">
+      <c r="F33" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="41">
-      <c r="A34" s="67" t="inlineStr">
+      <c r="A34" s="69" t="inlineStr">
         <is>
           <t>LessonPlanCompletion.js</t>
         </is>
       </c>
-      <c r="B34" s="70" t="inlineStr">
+      <c r="B34" s="72" t="inlineStr">
         <is>
           <t>Lesson completion track</t>
         </is>
       </c>
-      <c r="C34" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D34" s="69" t="inlineStr">
+      <c r="C34" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D34" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E34" s="70" t="inlineStr">
+      <c r="E34" s="72" t="inlineStr">
         <is>
           <t>lessonPlanRoutes.js</t>
         </is>
       </c>
-      <c r="F34" s="70" t="inlineStr">
+      <c r="F34" s="72" t="inlineStr">
         <is>
           <t>Tracked</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="41">
-      <c r="A35" s="67" t="inlineStr">
+      <c r="A35" s="69" t="inlineStr">
         <is>
           <t>ReportCardTemplate.js</t>
         </is>
       </c>
-      <c r="B35" s="70" t="inlineStr">
+      <c r="B35" s="72" t="inlineStr">
         <is>
           <t>Report card template</t>
         </is>
       </c>
-      <c r="C35" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D35" s="69" t="inlineStr">
+      <c r="C35" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D35" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E35" s="70" t="inlineStr">
+      <c r="E35" s="72" t="inlineStr">
         <is>
           <t>reportRoutes.js</t>
         </is>
       </c>
-      <c r="F35" s="70" t="inlineStr">
+      <c r="F35" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="41">
-      <c r="A36" s="67" t="inlineStr">
+      <c r="A36" s="69" t="inlineStr">
         <is>
           <t>TeachingMaterial.js</t>
         </is>
       </c>
-      <c r="B36" s="70" t="inlineStr">
+      <c r="B36" s="72" t="inlineStr">
         <is>
           <t>Teacher-uploaded material</t>
         </is>
       </c>
-      <c r="C36" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D36" s="69" t="inlineStr">
+      <c r="C36" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D36" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E36" s="70" t="inlineStr">
+      <c r="E36" s="72" t="inlineStr">
         <is>
           <t>teachingMaterialRoutes.js</t>
         </is>
       </c>
-      <c r="F36" s="70" t="inlineStr">
+      <c r="F36" s="72" t="inlineStr">
         <is>
           <t>Cloudinary + Qdrant ingest</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="41">
-      <c r="A37" s="67" t="inlineStr">
+      <c r="A37" s="69" t="inlineStr">
         <is>
           <t>Rubric.js</t>
         </is>
       </c>
-      <c r="B37" s="70" t="inlineStr">
+      <c r="B37" s="72" t="inlineStr">
         <is>
           <t>Grading rubric</t>
         </is>
       </c>
-      <c r="C37" s="63" t="inlineStr">
+      <c r="C37" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D37" s="64" t="inlineStr">
+      <c r="D37" s="66" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="E37" s="70" t="inlineStr">
+      <c r="E37" s="72" t="inlineStr">
         <is>
           <t>rubricRoutes.js</t>
         </is>
       </c>
-      <c r="F37" s="70" t="inlineStr">
+      <c r="F37" s="72" t="inlineStr">
         <is>
           <t>Rubric assignments now use the AI evaluator</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="41">
-      <c r="A38" s="67" t="inlineStr">
+      <c r="A38" s="69" t="inlineStr">
         <is>
           <t>PromotionHistory.js</t>
         </is>
       </c>
-      <c r="B38" s="70" t="inlineStr">
+      <c r="B38" s="72" t="inlineStr">
         <is>
           <t>Student promotion record</t>
         </is>
       </c>
-      <c r="C38" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D38" s="69" t="inlineStr">
+      <c r="C38" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D38" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E38" s="70" t="inlineStr">
+      <c r="E38" s="72" t="inlineStr">
         <is>
           <t>promotionRoutes.js</t>
         </is>
       </c>
-      <c r="F38" s="70" t="inlineStr">
+      <c r="F38" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
@@ -6260,672 +6273,672 @@
       <c r="F39" s="46" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="41">
-      <c r="A40" s="67" t="inlineStr">
+      <c r="A40" s="69" t="inlineStr">
         <is>
           <t>CurriculumMap.js</t>
         </is>
       </c>
-      <c r="B40" s="70" t="inlineStr">
+      <c r="B40" s="72" t="inlineStr">
         <is>
           <t>Topic prerequisite graph</t>
         </is>
       </c>
-      <c r="C40" s="63" t="inlineStr">
+      <c r="C40" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D40" s="64" t="inlineStr">
+      <c r="D40" s="66" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="E40" s="70" t="inlineStr">
+      <c r="E40" s="72" t="inlineStr">
         <is>
           <t>curriculumMapRoutes.js</t>
         </is>
       </c>
-      <c r="F40" s="70" t="inlineStr">
+      <c r="F40" s="72" t="inlineStr">
         <is>
           <t>Prerequisite traversal via gapDetectionEngine; no auto-update on ingest</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="41">
-      <c r="A41" s="67" t="inlineStr">
+      <c r="A41" s="69" t="inlineStr">
         <is>
           <t>MasteryScore.js</t>
         </is>
       </c>
-      <c r="B41" s="70" t="inlineStr">
+      <c r="B41" s="72" t="inlineStr">
         <is>
           <t>Per-topic mastery score</t>
         </is>
       </c>
-      <c r="C41" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D41" s="69" t="inlineStr">
+      <c r="C41" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D41" s="71" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E41" s="70" t="inlineStr">
+      <c r="E41" s="72" t="inlineStr">
         <is>
           <t>masteryRoutes.js</t>
         </is>
       </c>
-      <c r="F41" s="70" t="inlineStr">
+      <c r="F41" s="72" t="inlineStr">
         <is>
           <t>Auto-updated after baseline/tutor/practice/practice-paper/exam via masteryEventService</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="41">
-      <c r="A42" s="67" t="inlineStr">
+      <c r="A42" s="69" t="inlineStr">
         <is>
           <t>BaselineQuiz.js</t>
         </is>
       </c>
-      <c r="B42" s="70" t="inlineStr">
+      <c r="B42" s="72" t="inlineStr">
         <is>
           <t>Baseline quiz schema</t>
         </is>
       </c>
-      <c r="C42" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D42" s="69" t="inlineStr">
+      <c r="C42" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D42" s="71" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E42" s="70" t="inlineStr">
+      <c r="E42" s="72" t="inlineStr">
         <is>
           <t>baselineRoutes.js</t>
         </is>
       </c>
-      <c r="F42" s="70" t="inlineStr">
+      <c r="F42" s="72" t="inlineStr">
         <is>
           <t>Results feed mastery</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="41">
-      <c r="A43" s="67" t="inlineStr">
+      <c r="A43" s="69" t="inlineStr">
         <is>
           <t>BaselineResult.js</t>
         </is>
       </c>
-      <c r="B43" s="70" t="inlineStr">
+      <c r="B43" s="72" t="inlineStr">
         <is>
           <t>Baseline quiz result</t>
         </is>
       </c>
-      <c r="C43" s="63" t="inlineStr">
+      <c r="C43" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D43" s="64" t="inlineStr">
+      <c r="D43" s="66" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="E43" s="70" t="inlineStr">
+      <c r="E43" s="72" t="inlineStr">
         <is>
           <t>baselineRoutes.js</t>
         </is>
       </c>
-      <c r="F43" s="70" t="inlineStr">
+      <c r="F43" s="72" t="inlineStr">
         <is>
           <t>Wired to mastery update; consumer testing in progress</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="41">
-      <c r="A44" s="67" t="inlineStr">
+      <c r="A44" s="69" t="inlineStr">
         <is>
           <t>PracticePaper.js</t>
         </is>
       </c>
-      <c r="B44" s="70" t="inlineStr">
+      <c r="B44" s="72" t="inlineStr">
         <is>
           <t>Practice paper</t>
         </is>
       </c>
-      <c r="C44" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D44" s="69" t="inlineStr">
+      <c r="C44" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D44" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E44" s="70" t="inlineStr">
+      <c r="E44" s="72" t="inlineStr">
         <is>
           <t>practicePaperRoutes.js</t>
         </is>
       </c>
-      <c r="F44" s="70" t="inlineStr">
+      <c r="F44" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="41">
-      <c r="A45" s="67" t="inlineStr">
+      <c r="A45" s="69" t="inlineStr">
         <is>
           <t>PracticeQuestion.js</t>
         </is>
       </c>
-      <c r="B45" s="70" t="inlineStr">
+      <c r="B45" s="72" t="inlineStr">
         <is>
           <t>Practice question</t>
         </is>
       </c>
-      <c r="C45" s="63" t="inlineStr">
+      <c r="C45" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D45" s="64" t="inlineStr">
+      <c r="D45" s="66" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="E45" s="70" t="inlineStr">
+      <c r="E45" s="72" t="inlineStr">
         <is>
           <t>practiceRoutes.js</t>
         </is>
       </c>
-      <c r="F45" s="70" t="inlineStr">
+      <c r="F45" s="72" t="inlineStr">
         <is>
           <t>No Bloom level; not AI-auto-generated</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="41">
-      <c r="A46" s="67" t="inlineStr">
+      <c r="A46" s="69" t="inlineStr">
         <is>
           <t>PracticeSection.js</t>
         </is>
       </c>
-      <c r="B46" s="70" t="inlineStr">
+      <c r="B46" s="72" t="inlineStr">
         <is>
           <t>Practice paper section</t>
         </is>
       </c>
-      <c r="C46" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D46" s="69" t="inlineStr">
+      <c r="C46" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D46" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E46" s="70" t="inlineStr">
+      <c r="E46" s="72" t="inlineStr">
         <is>
           <t>practiceSectionRoutes.js</t>
         </is>
       </c>
-      <c r="F46" s="70" t="inlineStr">
+      <c r="F46" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="41">
-      <c r="A47" s="67" t="inlineStr">
+      <c r="A47" s="69" t="inlineStr">
         <is>
           <t>PracticeAttempt.js</t>
         </is>
       </c>
-      <c r="B47" s="70" t="inlineStr">
+      <c r="B47" s="72" t="inlineStr">
         <is>
           <t>Practice attempt</t>
         </is>
       </c>
-      <c r="C47" s="63" t="inlineStr">
+      <c r="C47" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D47" s="64" t="inlineStr">
+      <c r="D47" s="66" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="E47" s="70" t="inlineStr">
+      <c r="E47" s="72" t="inlineStr">
         <is>
           <t>practiceRoutes.js</t>
         </is>
       </c>
-      <c r="F47" s="70" t="inlineStr">
+      <c r="F47" s="72" t="inlineStr">
         <is>
           <t>Feeds mastery via shared assessment writer</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="41">
-      <c r="A48" s="67" t="inlineStr">
+      <c r="A48" s="69" t="inlineStr">
         <is>
           <t>TryoutResult.js</t>
         </is>
       </c>
-      <c r="B48" s="70" t="inlineStr">
+      <c r="B48" s="72" t="inlineStr">
         <is>
           <t>AI tryout result</t>
         </is>
       </c>
-      <c r="C48" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D48" s="69" t="inlineStr">
+      <c r="C48" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D48" s="71" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E48" s="70" t="inlineStr">
+      <c r="E48" s="72" t="inlineStr">
         <is>
           <t>aiLearningRoute.js</t>
         </is>
       </c>
-      <c r="F48" s="70" t="inlineStr">
+      <c r="F48" s="72" t="inlineStr">
         <is>
           <t>Feeds mastery</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="41">
-      <c r="A49" s="67" t="inlineStr">
+      <c r="A49" s="69" t="inlineStr">
         <is>
           <t>FlashcardResult.js</t>
         </is>
       </c>
-      <c r="B49" s="70" t="inlineStr">
+      <c r="B49" s="72" t="inlineStr">
         <is>
           <t>Flashcard rating result</t>
         </is>
       </c>
-      <c r="C49" s="63" t="inlineStr">
+      <c r="C49" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D49" s="64" t="inlineStr">
+      <c r="D49" s="66" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="E49" s="70" t="inlineStr">
+      <c r="E49" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F49" s="70" t="inlineStr">
+      <c r="F49" s="72" t="inlineStr">
         <is>
           <t>Ratings persist via applyAssessment; dedicated result rows not used from UI</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="41">
-      <c r="A50" s="67" t="inlineStr">
+      <c r="A50" s="69" t="inlineStr">
         <is>
           <t>ExternalResource.js</t>
         </is>
       </c>
-      <c r="B50" s="70" t="inlineStr">
+      <c r="B50" s="72" t="inlineStr">
         <is>
           <t>External study links</t>
         </is>
       </c>
-      <c r="C50" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D50" s="69" t="inlineStr">
+      <c r="C50" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D50" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E50" s="70" t="inlineStr">
+      <c r="E50" s="72" t="inlineStr">
         <is>
           <t>externalResourceRoutes.js</t>
         </is>
       </c>
-      <c r="F50" s="70" t="inlineStr">
+      <c r="F50" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="41">
-      <c r="A51" s="67" t="inlineStr">
+      <c r="A51" s="69" t="inlineStr">
         <is>
           <t>SpacedRepetitionSchedule.js</t>
         </is>
       </c>
-      <c r="B51" s="70" t="inlineStr">
+      <c r="B51" s="72" t="inlineStr">
         <is>
           <t>SM-2 review schedule</t>
         </is>
       </c>
-      <c r="C51" s="63" t="inlineStr">
+      <c r="C51" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D51" s="64" t="inlineStr">
+      <c r="D51" s="66" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="E51" s="70" t="inlineStr">
+      <c r="E51" s="72" t="inlineStr">
         <is>
           <t>spacedRepetitionRoutes.js</t>
         </is>
       </c>
-      <c r="F51" s="70" t="inlineStr">
+      <c r="F51" s="72" t="inlineStr">
         <is>
           <t>SM-2 + cron nudges + recommendation tie-in; not auto-triggered from every result</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="41">
-      <c r="A52" s="67" t="inlineStr">
+      <c r="A52" s="69" t="inlineStr">
         <is>
           <t>TeacherLearningPath.js</t>
         </is>
       </c>
-      <c r="B52" s="70" t="inlineStr">
+      <c r="B52" s="72" t="inlineStr">
         <is>
           <t>Teacher learning path</t>
         </is>
       </c>
-      <c r="C52" s="63" t="inlineStr">
+      <c r="C52" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D52" s="64" t="inlineStr">
+      <c r="D52" s="66" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="E52" s="70" t="inlineStr">
+      <c r="E52" s="72" t="inlineStr">
         <is>
           <t>learningPathRoutes.js</t>
         </is>
       </c>
-      <c r="F52" s="70" t="inlineStr">
+      <c r="F52" s="72" t="inlineStr">
         <is>
           <t>Manual paths; weekly AI study-plan generated separately</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="41">
-      <c r="A53" s="67" t="inlineStr">
+      <c r="A53" s="69" t="inlineStr">
         <is>
           <t>StudentProgress.js</t>
         </is>
       </c>
-      <c r="B53" s="70" t="inlineStr">
+      <c r="B53" s="72" t="inlineStr">
         <is>
           <t>Student progress snapshot</t>
         </is>
       </c>
-      <c r="C53" s="63" t="inlineStr">
+      <c r="C53" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D53" s="64" t="inlineStr">
+      <c r="D53" s="66" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="E53" s="70" t="inlineStr">
+      <c r="E53" s="72" t="inlineStr">
         <is>
           <t>progressRoute.js</t>
         </is>
       </c>
-      <c r="F53" s="70" t="inlineStr">
+      <c r="F53" s="72" t="inlineStr">
         <is>
           <t>Feeds analytics + forecast; reconciliation sweep every 15 min</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="41">
-      <c r="A54" s="67" t="inlineStr">
+      <c r="A54" s="69" t="inlineStr">
         <is>
           <t>StudentMemorySummary.js</t>
         </is>
       </c>
-      <c r="B54" s="70" t="inlineStr">
+      <c r="B54" s="72" t="inlineStr">
         <is>
           <t>AI student memory summary</t>
         </is>
       </c>
-      <c r="C54" s="63" t="inlineStr">
+      <c r="C54" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D54" s="64" t="inlineStr">
+      <c r="D54" s="66" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="E54" s="70" t="inlineStr">
+      <c r="E54" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F54" s="70" t="inlineStr">
+      <c r="F54" s="72" t="inlineStr">
         <is>
           <t>Rolling session-summarise; retention policy incomplete</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="41">
-      <c r="A55" s="67" t="inlineStr">
+      <c r="A55" s="69" t="inlineStr">
         <is>
           <t>TutorConversation.js</t>
         </is>
       </c>
-      <c r="B55" s="70" t="inlineStr">
+      <c r="B55" s="72" t="inlineStr">
         <is>
           <t>AI tutor chat session</t>
         </is>
       </c>
-      <c r="C55" s="63" t="inlineStr">
+      <c r="C55" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D55" s="64" t="inlineStr">
+      <c r="D55" s="66" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="E55" s="70" t="inlineStr">
+      <c r="E55" s="72" t="inlineStr">
         <is>
           <t>aiTutorRoutes.js</t>
         </is>
       </c>
-      <c r="F55" s="70" t="inlineStr">
+      <c r="F55" s="72" t="inlineStr">
         <is>
           <t>Persisted + teacher corrections joined on read; cross-session recall via summary only</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="41">
-      <c r="A56" s="67" t="inlineStr">
+      <c r="A56" s="69" t="inlineStr">
         <is>
           <t>ReadingMaterial.js</t>
         </is>
       </c>
-      <c r="B56" s="70" t="inlineStr">
+      <c r="B56" s="72" t="inlineStr">
         <is>
           <t>Reading passage upload</t>
         </is>
       </c>
-      <c r="C56" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D56" s="69" t="inlineStr">
+      <c r="C56" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D56" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E56" s="70" t="inlineStr">
+      <c r="E56" s="72" t="inlineStr">
         <is>
           <t>readingAssessmentRoutes.js</t>
         </is>
       </c>
-      <c r="F56" s="70" t="inlineStr">
+      <c r="F56" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="41">
-      <c r="A57" s="67" t="inlineStr">
+      <c r="A57" s="69" t="inlineStr">
         <is>
           <t>ReadingAssessment.js</t>
         </is>
       </c>
-      <c r="B57" s="70" t="inlineStr">
+      <c r="B57" s="72" t="inlineStr">
         <is>
           <t>Reading attempt + scores</t>
         </is>
       </c>
-      <c r="C57" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D57" s="69" t="inlineStr">
+      <c r="C57" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D57" s="71" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="E57" s="70" t="inlineStr">
+      <c r="E57" s="72" t="inlineStr">
         <is>
           <t>readingAssessmentRoutes.js</t>
         </is>
       </c>
-      <c r="F57" s="70" t="inlineStr">
+      <c r="F57" s="72" t="inlineStr">
         <is>
           <t>End-to-end pipeline working</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="41">
-      <c r="A58" s="67" t="inlineStr">
+      <c r="A58" s="69" t="inlineStr">
         <is>
           <t>WritingPrompt.js</t>
         </is>
       </c>
-      <c r="B58" s="70" t="inlineStr">
+      <c r="B58" s="72" t="inlineStr">
         <is>
           <t>Writing prompt upload</t>
         </is>
       </c>
-      <c r="C58" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D58" s="69" t="inlineStr">
+      <c r="C58" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D58" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E58" s="70" t="inlineStr">
+      <c r="E58" s="72" t="inlineStr">
         <is>
           <t>writingAssessmentRoutes.js</t>
         </is>
       </c>
-      <c r="F58" s="70" t="inlineStr">
+      <c r="F58" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="41">
-      <c r="A59" s="67" t="inlineStr">
+      <c r="A59" s="69" t="inlineStr">
         <is>
           <t>WritingAssessment.js</t>
         </is>
       </c>
-      <c r="B59" s="70" t="inlineStr">
+      <c r="B59" s="72" t="inlineStr">
         <is>
           <t>Writing submission + scores</t>
         </is>
       </c>
-      <c r="C59" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D59" s="69" t="inlineStr">
+      <c r="C59" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D59" s="71" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="E59" s="70" t="inlineStr">
+      <c r="E59" s="72" t="inlineStr">
         <is>
           <t>writingAssessmentRoutes.js</t>
         </is>
       </c>
-      <c r="F59" s="70" t="inlineStr">
+      <c r="F59" s="72" t="inlineStr">
         <is>
           <t>End-to-end pipeline working</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="41">
-      <c r="A60" s="67" t="inlineStr">
+      <c r="A60" s="69" t="inlineStr">
         <is>
           <t>StudentLanguageProfile.js</t>
         </is>
       </c>
-      <c r="B60" s="70" t="inlineStr">
+      <c r="B60" s="72" t="inlineStr">
         <is>
           <t>Adaptive language profile</t>
         </is>
       </c>
-      <c r="C60" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D60" s="69" t="inlineStr">
+      <c r="C60" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D60" s="71" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E60" s="70" t="inlineStr">
+      <c r="E60" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F60" s="70" t="inlineStr">
+      <c r="F60" s="72" t="inlineStr">
         <is>
           <t>Qdrant memory active</t>
         </is>
@@ -6944,224 +6957,224 @@
       <c r="F61" s="46" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1" s="41">
-      <c r="A62" s="67" t="inlineStr">
+      <c r="A62" s="69" t="inlineStr">
         <is>
           <t>StudentBadge.js</t>
         </is>
       </c>
-      <c r="B62" s="70" t="inlineStr">
+      <c r="B62" s="72" t="inlineStr">
         <is>
           <t>Achievement badge</t>
         </is>
       </c>
-      <c r="C62" s="63" t="inlineStr">
+      <c r="C62" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D62" s="64" t="inlineStr">
+      <c r="D62" s="66" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="E62" s="70" t="inlineStr">
+      <c r="E62" s="72" t="inlineStr">
         <is>
           <t>achievementRoutes.js</t>
         </is>
       </c>
-      <c r="F62" s="70" t="inlineStr">
+      <c r="F62" s="72" t="inlineStr">
         <is>
           <t>masteryEngine award logic; full auto-award UI pending</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="41">
-      <c r="A63" s="67" t="inlineStr">
+      <c r="A63" s="69" t="inlineStr">
         <is>
           <t>StudentJournalEntry.js</t>
         </is>
       </c>
-      <c r="B63" s="70" t="inlineStr">
+      <c r="B63" s="72" t="inlineStr">
         <is>
           <t>Personal journal</t>
         </is>
       </c>
-      <c r="C63" s="63" t="inlineStr">
+      <c r="C63" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D63" s="64" t="inlineStr">
+      <c r="D63" s="66" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="E63" s="70" t="inlineStr">
+      <c r="E63" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F63" s="70" t="inlineStr">
+      <c r="F63" s="72" t="inlineStr">
         <is>
           <t>Model only; no UI</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="41">
-      <c r="A64" s="67" t="inlineStr">
+      <c r="A64" s="69" t="inlineStr">
         <is>
           <t>StudentObservation.js</t>
         </is>
       </c>
-      <c r="B64" s="70" t="inlineStr">
+      <c r="B64" s="72" t="inlineStr">
         <is>
           <t>Teacher observation note</t>
         </is>
       </c>
-      <c r="C64" s="63" t="inlineStr">
+      <c r="C64" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D64" s="64" t="inlineStr">
+      <c r="D64" s="66" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="E64" s="70" t="inlineStr">
+      <c r="E64" s="72" t="inlineStr">
         <is>
           <t>studentObservationRoutes.js</t>
         </is>
       </c>
-      <c r="F64" s="70" t="inlineStr">
+      <c r="F64" s="72" t="inlineStr">
         <is>
           <t>Not linked to intervention</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="41">
-      <c r="A65" s="67" t="inlineStr">
+      <c r="A65" s="69" t="inlineStr">
         <is>
           <t>Wellbeing.js</t>
         </is>
       </c>
-      <c r="B65" s="70" t="inlineStr">
+      <c r="B65" s="72" t="inlineStr">
         <is>
           <t>Wellbeing check-in</t>
         </is>
       </c>
-      <c r="C65" s="63" t="inlineStr">
+      <c r="C65" s="65" t="inlineStr">
         <is>
           <t>🔶 Partial</t>
         </is>
       </c>
-      <c r="D65" s="64" t="inlineStr">
+      <c r="D65" s="66" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="E65" s="70" t="inlineStr">
+      <c r="E65" s="72" t="inlineStr">
         <is>
           <t>wellbeingRoute.js</t>
         </is>
       </c>
-      <c r="F65" s="70" t="inlineStr">
+      <c r="F65" s="72" t="inlineStr">
         <is>
           <t>No safeguard/escalation layer</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="41">
-      <c r="A66" s="67" t="inlineStr">
+      <c r="A66" s="69" t="inlineStr">
         <is>
           <t>InterventionLog.js</t>
         </is>
       </c>
-      <c r="B66" s="70" t="inlineStr">
+      <c r="B66" s="72" t="inlineStr">
         <is>
           <t>Teacher intervention record</t>
         </is>
       </c>
-      <c r="C66" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D66" s="69" t="inlineStr">
+      <c r="C66" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D66" s="71" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E66" s="70" t="inlineStr">
+      <c r="E66" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F66" s="70" t="inlineStr">
+      <c r="F66" s="72" t="inlineStr">
         <is>
           <t>Auto follow-up checkpoints + plan templates + automatic improvement + auto-finalize</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="41">
-      <c r="A67" s="67" t="inlineStr">
+      <c r="A67" s="69" t="inlineStr">
         <is>
           <t>Behaviour.js</t>
         </is>
       </c>
-      <c r="B67" s="70" t="inlineStr">
+      <c r="B67" s="72" t="inlineStr">
         <is>
           <t>Behaviour incident</t>
         </is>
       </c>
-      <c r="C67" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D67" s="69" t="inlineStr">
+      <c r="C67" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D67" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E67" s="70" t="inlineStr">
+      <c r="E67" s="72" t="inlineStr">
         <is>
           <t>behaviourRoute.js</t>
         </is>
       </c>
-      <c r="F67" s="70" t="inlineStr">
+      <c r="F67" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="41">
-      <c r="A68" s="67" t="inlineStr">
+      <c r="A68" s="69" t="inlineStr">
         <is>
           <t>ExcuseLetter.js</t>
         </is>
       </c>
-      <c r="B68" s="70" t="inlineStr">
+      <c r="B68" s="72" t="inlineStr">
         <is>
           <t>Excuse letter submission</t>
         </is>
       </c>
-      <c r="C68" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D68" s="69" t="inlineStr">
+      <c r="C68" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D68" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E68" s="70" t="inlineStr">
+      <c r="E68" s="72" t="inlineStr">
         <is>
           <t>excuseLetterRoutes.js</t>
         </is>
       </c>
-      <c r="F68" s="70" t="inlineStr">
+      <c r="F68" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
@@ -7180,384 +7193,384 @@
       <c r="F69" s="46" t="n"/>
     </row>
     <row r="70" ht="15" customHeight="1" s="41">
-      <c r="A70" s="67" t="inlineStr">
+      <c r="A70" s="69" t="inlineStr">
         <is>
           <t>ChatThread.js</t>
         </is>
       </c>
-      <c r="B70" s="70" t="inlineStr">
+      <c r="B70" s="72" t="inlineStr">
         <is>
           <t>Real-time chat thread</t>
         </is>
       </c>
-      <c r="C70" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D70" s="69" t="inlineStr">
+      <c r="C70" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D70" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E70" s="70" t="inlineStr">
+      <c r="E70" s="72" t="inlineStr">
         <is>
           <t>chatRoutes.js</t>
         </is>
       </c>
-      <c r="F70" s="70" t="inlineStr">
+      <c r="F70" s="72" t="inlineStr">
         <is>
           <t>Socket.IO active</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="41">
-      <c r="A71" s="67" t="inlineStr">
+      <c r="A71" s="69" t="inlineStr">
         <is>
           <t>ChatMessage.js</t>
         </is>
       </c>
-      <c r="B71" s="70" t="inlineStr">
+      <c r="B71" s="72" t="inlineStr">
         <is>
           <t>Chat message</t>
         </is>
       </c>
-      <c r="C71" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D71" s="69" t="inlineStr">
+      <c r="C71" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D71" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E71" s="70" t="inlineStr">
+      <c r="E71" s="72" t="inlineStr">
         <is>
           <t>chatRoutes.js</t>
         </is>
       </c>
-      <c r="F71" s="70" t="inlineStr">
+      <c r="F71" s="72" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="41">
-      <c r="A72" s="67" t="inlineStr">
+      <c r="A72" s="69" t="inlineStr">
         <is>
           <t>Notification.js</t>
         </is>
       </c>
-      <c r="B72" s="70" t="inlineStr">
+      <c r="B72" s="72" t="inlineStr">
         <is>
           <t>Push notification</t>
         </is>
       </c>
-      <c r="C72" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D72" s="69" t="inlineStr">
+      <c r="C72" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D72" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E72" s="70" t="inlineStr">
+      <c r="E72" s="72" t="inlineStr">
         <is>
           <t>notificationRoutes.js</t>
         </is>
       </c>
-      <c r="F72" s="70" t="inlineStr">
+      <c r="F72" s="72" t="inlineStr">
         <is>
           <t>Web push + in-app</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="41">
-      <c r="A73" s="67" t="inlineStr">
+      <c r="A73" s="69" t="inlineStr">
         <is>
           <t>PushSubscription.js</t>
         </is>
       </c>
-      <c r="B73" s="70" t="inlineStr">
+      <c r="B73" s="72" t="inlineStr">
         <is>
           <t>Browser push sub</t>
         </is>
       </c>
-      <c r="C73" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D73" s="69" t="inlineStr">
+      <c r="C73" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D73" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E73" s="70" t="inlineStr">
+      <c r="E73" s="72" t="inlineStr">
         <is>
           <t>notificationRoutes.js</t>
         </is>
       </c>
-      <c r="F73" s="70" t="inlineStr">
+      <c r="F73" s="72" t="inlineStr">
         <is>
           <t>VAPID keys active</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="41">
-      <c r="A74" s="67" t="inlineStr">
+      <c r="A74" s="69" t="inlineStr">
         <is>
           <t>AlcovePost.js</t>
         </is>
       </c>
-      <c r="B74" s="70" t="inlineStr">
+      <c r="B74" s="72" t="inlineStr">
         <is>
           <t>Academic Alcove post</t>
         </is>
       </c>
-      <c r="C74" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D74" s="69" t="inlineStr">
+      <c r="C74" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D74" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E74" s="70" t="inlineStr">
+      <c r="E74" s="72" t="inlineStr">
         <is>
           <t>alcoveRoute.js</t>
         </is>
       </c>
-      <c r="F74" s="70" t="inlineStr">
+      <c r="F74" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="41">
-      <c r="A75" s="67" t="inlineStr">
+      <c r="A75" s="69" t="inlineStr">
         <is>
           <t>AlcoveComment.js</t>
         </is>
       </c>
-      <c r="B75" s="70" t="inlineStr">
+      <c r="B75" s="72" t="inlineStr">
         <is>
           <t>Alcove comment</t>
         </is>
       </c>
-      <c r="C75" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D75" s="69" t="inlineStr">
+      <c r="C75" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D75" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E75" s="70" t="inlineStr">
+      <c r="E75" s="72" t="inlineStr">
         <is>
           <t>alcoveRoute.js</t>
         </is>
       </c>
-      <c r="F75" s="70" t="inlineStr">
+      <c r="F75" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="41">
-      <c r="A76" s="67" t="inlineStr">
+      <c r="A76" s="69" t="inlineStr">
         <is>
           <t>AlcoveSubmission.js</t>
         </is>
       </c>
-      <c r="B76" s="70" t="inlineStr">
+      <c r="B76" s="72" t="inlineStr">
         <is>
           <t>Alcove submission</t>
         </is>
       </c>
-      <c r="C76" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D76" s="69" t="inlineStr">
+      <c r="C76" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D76" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E76" s="70" t="inlineStr">
+      <c r="E76" s="72" t="inlineStr">
         <is>
           <t>alcoveRoute.js</t>
         </is>
       </c>
-      <c r="F76" s="70" t="inlineStr">
+      <c r="F76" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="41">
-      <c r="A77" s="67" t="inlineStr">
+      <c r="A77" s="69" t="inlineStr">
         <is>
           <t>FeeStructure.js</t>
         </is>
       </c>
-      <c r="B77" s="70" t="inlineStr">
+      <c r="B77" s="72" t="inlineStr">
         <is>
           <t>Fee structure</t>
         </is>
       </c>
-      <c r="C77" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D77" s="69" t="inlineStr">
+      <c r="C77" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D77" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E77" s="70" t="inlineStr">
+      <c r="E77" s="72" t="inlineStr">
         <is>
           <t>feeRoutes.js</t>
         </is>
       </c>
-      <c r="F77" s="70" t="inlineStr">
+      <c r="F77" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="41">
-      <c r="A78" s="67" t="inlineStr">
+      <c r="A78" s="69" t="inlineStr">
         <is>
           <t>FeeInvoice.js</t>
         </is>
       </c>
-      <c r="B78" s="70" t="inlineStr">
+      <c r="B78" s="72" t="inlineStr">
         <is>
           <t>Fee invoice</t>
         </is>
       </c>
-      <c r="C78" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D78" s="69" t="inlineStr">
+      <c r="C78" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D78" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E78" s="70" t="inlineStr">
+      <c r="E78" s="72" t="inlineStr">
         <is>
           <t>feeRoutes.js</t>
         </is>
       </c>
-      <c r="F78" s="70" t="inlineStr">
+      <c r="F78" s="72" t="inlineStr">
         <is>
           <t>Full CRUD</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="41">
-      <c r="A79" s="67" t="inlineStr">
+      <c r="A79" s="69" t="inlineStr">
         <is>
           <t>FeePayment.js</t>
         </is>
       </c>
-      <c r="B79" s="70" t="inlineStr">
+      <c r="B79" s="72" t="inlineStr">
         <is>
           <t>Razorpay payment</t>
         </is>
       </c>
-      <c r="C79" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D79" s="69" t="inlineStr">
+      <c r="C79" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D79" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E79" s="70" t="inlineStr">
+      <c r="E79" s="72" t="inlineStr">
         <is>
           <t>feeRoutes.js</t>
         </is>
       </c>
-      <c r="F79" s="70" t="inlineStr">
+      <c r="F79" s="72" t="inlineStr">
         <is>
           <t>Razorpay integrated</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="41">
-      <c r="A80" s="67" t="inlineStr">
+      <c r="A80" s="69" t="inlineStr">
         <is>
           <t>PaymentAudit.js</t>
         </is>
       </c>
-      <c r="B80" s="70" t="inlineStr">
+      <c r="B80" s="72" t="inlineStr">
         <is>
           <t>Payment audit trail</t>
         </is>
       </c>
-      <c r="C80" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D80" s="69" t="inlineStr">
+      <c r="C80" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D80" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E80" s="70" t="inlineStr">
+      <c r="E80" s="72" t="inlineStr">
         <is>
           <t>paymentSettingsRoutes.js</t>
         </is>
       </c>
-      <c r="F80" s="70" t="inlineStr">
+      <c r="F80" s="72" t="inlineStr">
         <is>
           <t>Full audit log</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="41">
-      <c r="A81" s="67" t="inlineStr">
+      <c r="A81" s="69" t="inlineStr">
         <is>
           <t>AuditLog.js</t>
         </is>
       </c>
-      <c r="B81" s="70" t="inlineStr">
+      <c r="B81" s="72" t="inlineStr">
         <is>
           <t>System audit log</t>
         </is>
       </c>
-      <c r="C81" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D81" s="69" t="inlineStr">
+      <c r="C81" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D81" s="71" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E81" s="70" t="inlineStr">
+      <c r="E81" s="72" t="inlineStr">
         <is>
           <t>auditLogRoutes.js</t>
         </is>
       </c>
-      <c r="F81" s="70" t="inlineStr">
+      <c r="F81" s="72" t="inlineStr">
         <is>
           <t>All key events logged</t>
         </is>
@@ -7581,12 +7594,12 @@
           <t>Immutable mastery-change audit</t>
         </is>
       </c>
-      <c r="C84" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D84" s="71" t="inlineStr">
+      <c r="C84" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D84" s="73" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -7613,12 +7626,12 @@
           <t>Transactional score+event writer</t>
         </is>
       </c>
-      <c r="C85" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D85" s="71" t="inlineStr">
+      <c r="C85" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D85" s="73" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -7645,12 +7658,12 @@
           <t>At-risk / gap / milestone records</t>
         </is>
       </c>
-      <c r="C86" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D86" s="71" t="inlineStr">
+      <c r="C86" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D86" s="73" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -7677,12 +7690,12 @@
           <t>Persisted weekly study plan</t>
         </is>
       </c>
-      <c r="C87" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D87" s="71" t="inlineStr">
+      <c r="C87" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D87" s="73" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -7709,12 +7722,12 @@
           <t>AI-generated question bank</t>
         </is>
       </c>
-      <c r="C88" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D88" s="71" t="inlineStr">
+      <c r="C88" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D88" s="73" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -7741,12 +7754,12 @@
           <t>Per-answer error classification</t>
         </is>
       </c>
-      <c r="C89" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D89" s="71" t="inlineStr">
+      <c r="C89" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D89" s="73" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -7773,12 +7786,12 @@
           <t>Recommendation lifecycle + impact</t>
         </is>
       </c>
-      <c r="C90" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D90" s="71" t="inlineStr">
+      <c r="C90" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D90" s="73" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -7805,12 +7818,12 @@
           <t>Teacher override of an AI answer</t>
         </is>
       </c>
-      <c r="C91" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D91" s="71" t="inlineStr">
+      <c r="C91" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D91" s="73" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -7837,12 +7850,12 @@
           <t>Teacher-assigned written question</t>
         </is>
       </c>
-      <c r="C92" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D92" s="71" t="inlineStr">
+      <c r="C92" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D92" s="73" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -7869,12 +7882,12 @@
           <t>Student written answer + AI grade + review</t>
         </is>
       </c>
-      <c r="C93" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D93" s="71" t="inlineStr">
+      <c r="C93" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D93" s="73" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -7901,12 +7914,12 @@
           <t>Per-student misconception model</t>
         </is>
       </c>
-      <c r="C94" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D94" s="71" t="inlineStr">
+      <c r="C94" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D94" s="73" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -7933,12 +7946,12 @@
           <t>Adaptive practice difficulty rung</t>
         </is>
       </c>
-      <c r="C95" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D95" s="71" t="inlineStr">
+      <c r="C95" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D95" s="73" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -7965,12 +7978,12 @@
           <t>Pre/post outcome measurement</t>
         </is>
       </c>
-      <c r="C96" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="D96" s="71" t="inlineStr">
+      <c r="C96" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="D96" s="73" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8074,384 +8087,384 @@
       <c r="F4" s="46" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="41">
-      <c r="A5" s="67" t="inlineStr">
+      <c r="A5" s="69" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="B5" s="70" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>Document ingestion</t>
         </is>
       </c>
-      <c r="C5" s="70" t="inlineStr">
+      <c r="C5" s="72" t="inlineStr">
         <is>
           <t>OCR → parse → chunk → embed → Qdrant upsert</t>
         </is>
       </c>
-      <c r="D5" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E5" s="68" t="inlineStr">
+      <c r="D5" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E5" s="70" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="F5" s="70" t="inlineStr">
+      <c r="F5" s="72" t="inlineStr">
         <is>
           <t>OCR/parse/chunk/embed/upsert + Bloom/outcome/topic tagging on ingest</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="41">
-      <c r="A6" s="67" t="inlineStr">
+      <c r="A6" s="69" t="inlineStr">
         <is>
           <t>parser</t>
         </is>
       </c>
-      <c r="B6" s="70" t="inlineStr">
+      <c r="B6" s="72" t="inlineStr">
         <is>
           <t>Text extract + cleaner</t>
         </is>
       </c>
-      <c r="C6" s="70" t="inlineStr">
+      <c r="C6" s="72" t="inlineStr">
         <is>
           <t>PyMuPDF/Tesseract/docx/pptx; strip teacher notes</t>
         </is>
       </c>
-      <c r="D6" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E6" s="68" t="inlineStr">
+      <c r="D6" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E6" s="70" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="F6" s="70" t="inlineStr">
+      <c r="F6" s="72" t="inlineStr">
         <is>
           <t>_strip_teacher_notes + injection stripping active</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="41">
-      <c r="A7" s="67" t="inlineStr">
+      <c r="A7" s="69" t="inlineStr">
         <is>
           <t>embeddings</t>
         </is>
       </c>
-      <c r="B7" s="70" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>Embedding generation</t>
         </is>
       </c>
-      <c r="C7" s="70" t="inlineStr">
+      <c r="C7" s="72" t="inlineStr">
         <is>
           <t>nomic-embed-text → Qdrant</t>
         </is>
       </c>
-      <c r="D7" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E7" s="68" t="inlineStr">
+      <c r="D7" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E7" s="70" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="F7" s="70" t="inlineStr">
+      <c r="F7" s="72" t="inlineStr">
         <is>
           <t>Fully wired</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="41">
-      <c r="A8" s="67" t="inlineStr">
+      <c r="A8" s="69" t="inlineStr">
         <is>
           <t>retrieval</t>
         </is>
       </c>
-      <c r="B8" s="70" t="inlineStr">
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>Semantic retrieval</t>
         </is>
       </c>
-      <c r="C8" s="70" t="inlineStr">
+      <c r="C8" s="72" t="inlineStr">
         <is>
           <t>Qdrant metadata filters: school/class/section/subject/chapter</t>
         </is>
       </c>
-      <c r="D8" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E8" s="68" t="inlineStr">
+      <c r="D8" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E8" s="70" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="F8" s="70" t="inlineStr">
+      <c r="F8" s="72" t="inlineStr">
         <is>
           <t>Metadata filters + hybrid BM25+semantic RRF + Bloom-level filter</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="41">
-      <c r="A9" s="67" t="inlineStr">
+      <c r="A9" s="69" t="inlineStr">
         <is>
           <t>chat</t>
         </is>
       </c>
-      <c r="B9" s="70" t="inlineStr">
+      <c r="B9" s="72" t="inlineStr">
         <is>
           <t>RAG tutor — all modes</t>
         </is>
       </c>
-      <c r="C9" s="70" t="inlineStr">
+      <c r="C9" s="72" t="inlineStr">
         <is>
           <t>explain/quiz/flashcards/notes/mindmap/summarize/homework_help</t>
         </is>
       </c>
-      <c r="D9" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E9" s="68" t="inlineStr">
+      <c r="D9" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E9" s="70" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="F9" s="70" t="inlineStr">
+      <c r="F9" s="72" t="inlineStr">
         <is>
           <t>All modes; file-based prompt library overrides inline MODE_INSTRUCTIONS</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="41">
-      <c r="A10" s="67" t="inlineStr">
+      <c r="A10" s="69" t="inlineStr">
         <is>
           <t>quiz</t>
         </is>
       </c>
-      <c r="B10" s="70" t="inlineStr">
+      <c r="B10" s="72" t="inlineStr">
         <is>
           <t>Quiz generation</t>
         </is>
       </c>
-      <c r="C10" s="70" t="inlineStr">
+      <c r="C10" s="72" t="inlineStr">
         <is>
           <t>5 MCQ per request via RAG</t>
         </is>
       </c>
-      <c r="D10" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E10" s="68" t="inlineStr">
+      <c r="D10" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E10" s="70" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
       </c>
-      <c r="F10" s="70" t="inlineStr">
+      <c r="F10" s="72" t="inlineStr">
         <is>
           <t>Bloom-target passed from mastery; not saved to question bank</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="41">
-      <c r="A11" s="67" t="inlineStr">
+      <c r="A11" s="69" t="inlineStr">
         <is>
           <t>flashcards</t>
         </is>
       </c>
-      <c r="B11" s="70" t="inlineStr">
+      <c r="B11" s="72" t="inlineStr">
         <is>
           <t>Flashcard generation</t>
         </is>
       </c>
-      <c r="C11" s="70" t="inlineStr">
+      <c r="C11" s="72" t="inlineStr">
         <is>
           <t>Q:/A: format via RAG</t>
         </is>
       </c>
-      <c r="D11" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E11" s="68" t="inlineStr">
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E11" s="70" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="F11" s="70" t="inlineStr">
+      <c r="F11" s="72" t="inlineStr">
         <is>
           <t>Ratings persist to mastery</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="41">
-      <c r="A12" s="67" t="inlineStr">
+      <c r="A12" s="69" t="inlineStr">
         <is>
           <t>summaries</t>
         </is>
       </c>
-      <c r="B12" s="70" t="inlineStr">
+      <c r="B12" s="72" t="inlineStr">
         <is>
           <t>Summary generation</t>
         </is>
       </c>
-      <c r="C12" s="70" t="inlineStr">
+      <c r="C12" s="72" t="inlineStr">
         <is>
           <t>Chapter summaries; OCR + summarize endpoint</t>
         </is>
       </c>
-      <c r="D12" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E12" s="68" t="inlineStr">
+      <c r="D12" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E12" s="70" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="F12" s="70" t="inlineStr">
+      <c r="F12" s="72" t="inlineStr">
         <is>
           <t>Working well</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="41">
-      <c r="A13" s="67" t="inlineStr">
+      <c r="A13" s="69" t="inlineStr">
         <is>
           <t>assessment</t>
         </is>
       </c>
-      <c r="B13" s="70" t="inlineStr">
+      <c r="B13" s="72" t="inlineStr">
         <is>
           <t>Language eval (Qwen3 8B)</t>
         </is>
       </c>
-      <c r="C13" s="70" t="inlineStr">
+      <c r="C13" s="72" t="inlineStr">
         <is>
           <t>Reading + writing rubric + score JSON</t>
         </is>
       </c>
-      <c r="D13" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E13" s="68" t="inlineStr">
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E13" s="70" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="F13" s="70" t="inlineStr">
+      <c r="F13" s="72" t="inlineStr">
         <is>
           <t>Reading + writing rubric scoring</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="41">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>speech</t>
         </is>
       </c>
-      <c r="B14" s="70" t="inlineStr">
+      <c r="B14" s="72" t="inlineStr">
         <is>
           <t>Audio transcription</t>
         </is>
       </c>
-      <c r="C14" s="70" t="inlineStr">
+      <c r="C14" s="72" t="inlineStr">
         <is>
           <t>faster-whisper + SpeechBrain pronunciation</t>
         </is>
       </c>
-      <c r="D14" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E14" s="68" t="inlineStr">
+      <c r="D14" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E14" s="70" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="F14" s="70" t="inlineStr">
+      <c r="F14" s="72" t="inlineStr">
         <is>
           <t>faster-whisper + wav2vec2 pronunciation</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="41">
-      <c r="A15" s="67" t="inlineStr">
+      <c r="A15" s="69" t="inlineStr">
         <is>
           <t>language_memory</t>
         </is>
       </c>
-      <c r="B15" s="70" t="inlineStr">
+      <c r="B15" s="72" t="inlineStr">
         <is>
           <t>Adaptive language memory</t>
         </is>
       </c>
-      <c r="C15" s="70" t="inlineStr">
+      <c r="C15" s="72" t="inlineStr">
         <is>
           <t>Qdrant student_language_memory; store/retrieve</t>
         </is>
       </c>
-      <c r="D15" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E15" s="68" t="inlineStr">
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E15" s="70" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
       </c>
-      <c r="F15" s="70" t="inlineStr">
+      <c r="F15" s="72" t="inlineStr">
         <is>
           <t>Qdrant student_language_memory store/retrieve</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="41">
-      <c r="A16" s="67" t="inlineStr">
+      <c r="A16" s="69" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="B16" s="70" t="inlineStr">
+      <c r="B16" s="72" t="inlineStr">
         <is>
           <t>Admin module</t>
         </is>
       </c>
-      <c r="C16" s="70" t="inlineStr">
+      <c r="C16" s="72" t="inlineStr">
         <is>
           <t>Admin-facing AI controls</t>
         </is>
       </c>
-      <c r="D16" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E16" s="68" t="inlineStr">
+      <c r="D16" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E16" s="70" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F16" s="70" t="inlineStr">
+      <c r="F16" s="72" t="inlineStr">
         <is>
           <t>4 report types (overview / dropout / teacher / integrity) with prompt builders synthesising mastery matrix, teacher effectiveness, dropout risk, cohort trend, content usage, exam integrity -&gt; executive summaries.</t>
         </is>
@@ -8470,288 +8483,288 @@
       <c r="F17" s="46" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="41">
-      <c r="A18" s="67" t="inlineStr">
+      <c r="A18" s="69" t="inlineStr">
         <is>
           <t>orchestrator</t>
         </is>
       </c>
-      <c r="B18" s="70" t="inlineStr">
+      <c r="B18" s="72" t="inlineStr">
         <is>
           <t>Central AI coordinator</t>
         </is>
       </c>
-      <c r="C18" s="70" t="inlineStr">
+      <c r="C18" s="72" t="inlineStr">
         <is>
           <t>Node → Orchestrator → engines</t>
         </is>
       </c>
-      <c r="D18" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E18" s="68" t="inlineStr">
+      <c r="D18" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E18" s="70" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="F18" s="70" t="inlineStr">
+      <c r="F18" s="72" t="inlineStr">
         <is>
           <t>POST /orchestrate dispatch — generate / generate_questions / evaluate / summarize_session / class_performance</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="41">
-      <c r="A19" s="67" t="inlineStr">
+      <c r="A19" s="69" t="inlineStr">
         <is>
           <t>knowledge_graph</t>
         </is>
       </c>
-      <c r="B19" s="70" t="inlineStr">
+      <c r="B19" s="72" t="inlineStr">
         <is>
           <t>Graph traversal</t>
         </is>
       </c>
-      <c r="C19" s="70" t="inlineStr">
+      <c r="C19" s="72" t="inlineStr">
         <is>
           <t>Kahn topo-sort, cycle detection, gap + root-cause traversal, bridge-path</t>
         </is>
       </c>
-      <c r="D19" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E19" s="68" t="inlineStr">
+      <c r="D19" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E19" s="70" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="F19" s="70" t="inlineStr">
+      <c r="F19" s="72" t="inlineStr">
         <is>
           <t>ai-service/app/modules/knowledge_graph/ — Kahn topo-sort + cycle detection + gap/root-cause traversal + prerequisite bridge-path. POST /knowledge-graph/analyze + orchestrator task_type graph_analyze + Node client. Tests: test_knowledge_graph.py, knowledgeGraphClient.test.js</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="41">
-      <c r="A20" s="67" t="inlineStr">
+      <c r="A20" s="69" t="inlineStr">
         <is>
           <t>bloom</t>
         </is>
       </c>
-      <c r="B20" s="70" t="inlineStr">
+      <c r="B20" s="72" t="inlineStr">
         <is>
           <t>Bloom classifier</t>
         </is>
       </c>
-      <c r="C20" s="70" t="inlineStr">
+      <c r="C20" s="72" t="inlineStr">
         <is>
           <t>Tag documents, questions, answers</t>
         </is>
       </c>
-      <c r="D20" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E20" s="68" t="inlineStr">
+      <c r="D20" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E20" s="70" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="F20" s="70" t="inlineStr">
+      <c r="F20" s="72" t="inlineStr">
         <is>
           <t>classifier/bloom.py — tags docs on ingest; question + retrieval integration</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="41">
-      <c r="A21" s="67" t="inlineStr">
+      <c r="A21" s="69" t="inlineStr">
         <is>
           <t>mastery_engine</t>
         </is>
       </c>
-      <c r="B21" s="70" t="inlineStr">
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>Mastery calculator</t>
         </is>
       </c>
-      <c r="C21" s="70" t="inlineStr">
+      <c r="C21" s="72" t="inlineStr">
         <is>
           <t>accuracy + attempts + time + recency; auto-update</t>
         </is>
       </c>
-      <c r="D21" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E21" s="68" t="inlineStr">
+      <c r="D21" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E21" s="70" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F21" s="70" t="inlineStr">
+      <c r="F21" s="72" t="inlineStr">
         <is>
           <t>N/A as an ai-service module — mastery calc is Node-side by design (masteryEngine.js + masteryEventService.js). Engine complete (feature #18).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="41">
-      <c r="A22" s="67" t="inlineStr">
+      <c r="A22" s="69" t="inlineStr">
         <is>
           <t>error_classifier</t>
         </is>
       </c>
-      <c r="B22" s="70" t="inlineStr">
+      <c r="B22" s="72" t="inlineStr">
         <is>
           <t>Error type classifier</t>
         </is>
       </c>
-      <c r="C22" s="70" t="inlineStr">
+      <c r="C22" s="72" t="inlineStr">
         <is>
           <t>Concept/Calculation/Reading/Logic</t>
         </is>
       </c>
-      <c r="D22" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E22" s="68" t="inlineStr">
+      <c r="D22" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E22" s="70" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F22" s="70" t="inlineStr">
+      <c r="F22" s="72" t="inlineStr">
         <is>
           <t>ai-service classifier + backend/services/errorClassifier.js</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="41">
-      <c r="A23" s="67" t="inlineStr">
+      <c r="A23" s="69" t="inlineStr">
         <is>
           <t>gap_detector</t>
         </is>
       </c>
-      <c r="B23" s="70" t="inlineStr">
+      <c r="B23" s="72" t="inlineStr">
         <is>
           <t>Gap detection</t>
         </is>
       </c>
-      <c r="C23" s="70" t="inlineStr">
+      <c r="C23" s="72" t="inlineStr">
         <is>
           <t>Prerequisite traversal → root-cause weak topic</t>
         </is>
       </c>
-      <c r="D23" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E23" s="68" t="inlineStr">
+      <c r="D23" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E23" s="70" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F23" s="70" t="inlineStr">
+      <c r="F23" s="72" t="inlineStr">
         <is>
           <t>In-process engine is Node-side (gapDetectionEngine.js); shared Python traversal now available via knowledge_graph module. Engine complete (feature #24).</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="41">
-      <c r="A24" s="67" t="inlineStr">
+      <c r="A24" s="69" t="inlineStr">
         <is>
           <t>recommendation</t>
         </is>
       </c>
-      <c r="B24" s="70" t="inlineStr">
+      <c r="B24" s="72" t="inlineStr">
         <is>
           <t>Recommendation engine</t>
         </is>
       </c>
-      <c r="C24" s="70" t="inlineStr">
+      <c r="C24" s="72" t="inlineStr">
         <is>
           <t>Next topic based on mastery + curriculum graph</t>
         </is>
       </c>
-      <c r="D24" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E24" s="68" t="inlineStr">
+      <c r="D24" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E24" s="70" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F24" s="70" t="inlineStr">
+      <c r="F24" s="72" t="inlineStr">
         <is>
           <t>N/A as an ai-service module — Node-side by design (recommendationEngine.js + recommendationImpactService.js). Engine complete (feature #25).</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="41">
-      <c r="A25" s="67" t="inlineStr">
+      <c r="A25" s="69" t="inlineStr">
         <is>
           <t>analytics</t>
         </is>
       </c>
-      <c r="B25" s="70" t="inlineStr">
+      <c r="B25" s="72" t="inlineStr">
         <is>
           <t>AI analytics insights</t>
         </is>
       </c>
-      <c r="C25" s="70" t="inlineStr">
+      <c r="C25" s="72" t="inlineStr">
         <is>
           <t>Per-topic heatmap; at-risk; AI narrative</t>
         </is>
       </c>
-      <c r="D25" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E25" s="68" t="inlineStr">
+      <c r="D25" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E25" s="70" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F25" s="70" t="inlineStr">
+      <c r="F25" s="72" t="inlineStr">
         <is>
           <t>N/A as an ai-service module — analytics is Node-side (classLearningAnalytics.js); AI narrative layer = the admin module above. Features #44, #49.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="41">
-      <c r="A26" s="67" t="inlineStr">
+      <c r="A26" s="69" t="inlineStr">
         <is>
           <t>prompt_library</t>
         </is>
       </c>
-      <c r="B26" s="70" t="inlineStr">
+      <c r="B26" s="72" t="inlineStr">
         <is>
           <t>Prompt directory</t>
         </is>
       </c>
-      <c r="C26" s="70" t="inlineStr">
+      <c r="C26" s="72" t="inlineStr">
         <is>
           <t>externalise all prompts from Python modules</t>
         </is>
       </c>
-      <c r="D26" s="68" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E26" s="68" t="inlineStr">
+      <c r="D26" s="70" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E26" s="70" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="F26" s="70" t="inlineStr">
+      <c r="F26" s="72" t="inlineStr">
         <is>
           <t>ai-service/prompts/ + loader.py (~50 files)</t>
         </is>
@@ -8780,12 +8793,12 @@
           <t>POST /evaluate/answer — marks, rubric, missing concepts, confidence</t>
         </is>
       </c>
-      <c r="D29" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E29" s="71" t="inlineStr">
+      <c r="D29" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E29" s="73" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -8812,12 +8825,12 @@
           <t>bloom.py + outcomes.py + topic.py — imported by documents + chat</t>
         </is>
       </c>
-      <c r="D30" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E30" s="71" t="inlineStr">
+      <c r="D30" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E30" s="73" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -8844,12 +8857,12 @@
           <t>service.py + verifier.py — arithmetic / unit checks</t>
         </is>
       </c>
-      <c r="D31" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E31" s="71" t="inlineStr">
+      <c r="D31" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E31" s="73" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -8876,12 +8889,12 @@
           <t>POST /vision/explain-image + PDF-page vision on ingest (client.py)</t>
         </is>
       </c>
-      <c r="D32" s="71" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="E32" s="71" t="inlineStr">
+      <c r="D32" s="73" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E32" s="73" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -8963,288 +8976,288 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="41">
-      <c r="A4" s="67" t="inlineStr">
+      <c r="A4" s="69" t="inlineStr">
         <is>
           <t>Core AI Pipeline</t>
         </is>
       </c>
-      <c r="B4" s="72" t="n">
+      <c r="B4" s="74" t="n">
         <v>6</v>
       </c>
-      <c r="C4" s="69" t="n">
+      <c r="C4" s="71" t="n">
         <v>6</v>
       </c>
-      <c r="D4" s="64" t="n">
+      <c r="D4" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="62" t="n">
+      <c r="E4" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="70" t="inlineStr">
+      <c r="F4" s="72" t="inlineStr">
         <is>
           <t>Done — orchestrator, hybrid search, prompt library all live</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="41">
-      <c r="A5" s="67" t="inlineStr">
+      <c r="A5" s="69" t="inlineStr">
         <is>
           <t>Content Intelligence</t>
         </is>
       </c>
-      <c r="B5" s="72" t="n">
+      <c r="B5" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="69" t="n">
+      <c r="C5" s="71" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="64" t="n">
+      <c r="D5" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="62" t="n">
+      <c r="E5" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="70" t="inlineStr">
+      <c r="F5" s="72" t="inlineStr">
         <is>
           <t>Re-index legacy chunks for Bloom/outcomes; finish doc-versioning UI</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="41">
-      <c r="A6" s="67" t="inlineStr">
+      <c r="A6" s="69" t="inlineStr">
         <is>
           <t>Assessment &amp; Evaluation</t>
         </is>
       </c>
-      <c r="B6" s="72" t="n">
+      <c r="B6" s="74" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="69" t="n">
+      <c r="C6" s="71" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="64" t="n">
+      <c r="D6" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="62" t="n">
+      <c r="E6" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="70" t="inlineStr">
+      <c r="F6" s="72" t="inlineStr">
         <is>
           <t>Live replica-set DB verification of the mastery/evaluator pipeline</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="41">
-      <c r="A7" s="67" t="inlineStr">
+      <c r="A7" s="69" t="inlineStr">
         <is>
           <t>Mastery &amp; Memory</t>
         </is>
       </c>
-      <c r="B7" s="72" t="n">
+      <c r="B7" s="74" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="69" t="n">
+      <c r="C7" s="71" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="64" t="n">
+      <c r="D7" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="62" t="n">
+      <c r="E7" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="70" t="inlineStr">
+      <c r="F7" s="72" t="inlineStr">
         <is>
           <t>Validate forecasts on longitudinal data; academic-memory retention policy</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="41">
-      <c r="A8" s="67" t="inlineStr">
+      <c r="A8" s="69" t="inlineStr">
         <is>
           <t>Gap &amp; Learning Path</t>
         </is>
       </c>
-      <c r="B8" s="72" t="n">
+      <c r="B8" s="74" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="69" t="n">
+      <c r="C8" s="71" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="64" t="n">
+      <c r="D8" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="62" t="n">
+      <c r="E8" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="70" t="inlineStr">
+      <c r="F8" s="72" t="inlineStr">
         <is>
           <t>Wire recommendation widget to accept/complete; AI bridge-path generation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="41">
-      <c r="A9" s="67" t="inlineStr">
+      <c r="A9" s="69" t="inlineStr">
         <is>
           <t>AI Content Generation (Student)</t>
         </is>
       </c>
-      <c r="B9" s="72" t="n">
+      <c r="B9" s="74" t="n">
         <v>9</v>
       </c>
-      <c r="C9" s="69" t="n">
+      <c r="C9" s="71" t="n">
         <v>9</v>
       </c>
-      <c r="D9" s="64" t="n">
+      <c r="D9" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="62" t="n">
+      <c r="E9" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="70" t="inlineStr">
+      <c r="F9" s="72" t="inlineStr">
         <is>
           <t>Personalise worksheets to mastery gaps; adaptive item selection</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="41">
-      <c r="A10" s="67" t="inlineStr">
+      <c r="A10" s="69" t="inlineStr">
         <is>
           <t>AI Content Generation (Teacher)</t>
         </is>
       </c>
-      <c r="B10" s="72" t="n">
+      <c r="B10" s="74" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="69" t="n">
+      <c r="C10" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="64" t="n">
+      <c r="D10" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="62" t="n">
+      <c r="E10" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="70" t="inlineStr">
+      <c r="F10" s="72" t="inlineStr">
         <is>
           <t>Teacher UI for Bloom/difficulty selection; surface override affordance</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="41">
-      <c r="A11" s="67" t="inlineStr">
+      <c r="A11" s="69" t="inlineStr">
         <is>
           <t>Language Assessment</t>
         </is>
       </c>
-      <c r="B11" s="72" t="n">
+      <c r="B11" s="74" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="69" t="n">
+      <c r="C11" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="64" t="n">
+      <c r="D11" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="62" t="n">
+      <c r="E11" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="70" t="inlineStr">
+      <c r="F11" s="72" t="inlineStr">
         <is>
           <t>Real-device mic testing; surface language profile card</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="41">
-      <c r="A12" s="67" t="inlineStr">
+      <c r="A12" s="69" t="inlineStr">
         <is>
           <t>Analytics &amp; Intelligence</t>
         </is>
       </c>
-      <c r="B12" s="72" t="n">
+      <c r="B12" s="74" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="69" t="n">
+      <c r="C12" s="71" t="n">
         <v>7</v>
       </c>
-      <c r="D12" s="64" t="n">
+      <c r="D12" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="62" t="n">
+      <c r="E12" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="70" t="inlineStr">
+      <c r="F12" s="72" t="inlineStr">
         <is>
           <t>Teacher dashboard cards for engagement + at-risk; narrative-quality eval</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="41">
-      <c r="A13" s="67" t="inlineStr">
+      <c r="A13" s="69" t="inlineStr">
         <is>
           <t>Research-Grade Features</t>
         </is>
       </c>
-      <c r="B13" s="72" t="n">
+      <c r="B13" s="74" t="n">
         <v>14</v>
       </c>
-      <c r="C13" s="69" t="n">
+      <c r="C13" s="71" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="64" t="n">
+      <c r="D13" s="66" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="62" t="n">
+      <c r="E13" s="64" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="70" t="inlineStr">
+      <c r="F13" s="72" t="inlineStr">
         <is>
           <t>Safety escalation + safeguarding + explainable-AI lineage</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="41">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>Future Features</t>
         </is>
       </c>
-      <c r="B14" s="72" t="n">
+      <c r="B14" s="74" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="69" t="n">
+      <c r="C14" s="71" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="64" t="n">
+      <c r="D14" s="66" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="62" t="n">
+      <c r="E14" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="70" t="inlineStr">
+      <c r="F14" s="72" t="inlineStr">
         <is>
           <t>Voice loop, student image upload, math step-solver UI</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="41">
-      <c r="A16" s="67" t="inlineStr">
+      <c r="A16" s="69" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="73" t="n">
+      <c r="B16" s="75" t="n">
         <v>73</v>
       </c>
-      <c r="C16" s="69" t="n">
+      <c r="C16" s="71" t="n">
         <v>54</v>
       </c>
-      <c r="D16" s="64" t="n">
+      <c r="D16" s="66" t="n">
         <v>10</v>
       </c>
-      <c r="E16" s="62" t="n">
+      <c r="E16" s="64" t="n">
         <v>9</v>
       </c>
-      <c r="F16" s="70" t="n"/>
+      <c r="F16" s="72" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="41">
       <c r="A17" s="40" t="inlineStr">
@@ -9254,36 +9267,36 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="41">
-      <c r="A18" s="74" t="n"/>
+      <c r="A18" s="76" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="41">
-      <c r="A20" s="75" t="inlineStr">
+      <c r="A20" s="77" t="inlineStr">
         <is>
           <t>Re-audited 2026-09-10 against the AI-layer build (see AI_UNTOUCHED_FEATURES_CHECKLIST.md)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="41">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="78" t="inlineStr">
         <is>
           <t>Core learning-intelligence engines (orchestrator, hybrid search, Bloom, error classifier, gap detection, mastery auto-update, recommendations, study plan) now built; remaining gaps concentrate in safety/governance, quality monitoring, and training-data infra</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="41">
-      <c r="A23" s="77" t="inlineStr">
+      <c r="A23" s="79" t="inlineStr">
         <is>
           <t>TOP 5 PRIORITIES (2026-09-10)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="41">
-      <c r="A24" s="67" t="inlineStr">
+      <c r="A24" s="69" t="inlineStr">
         <is>
           <t>1. Safety &amp; governance layer</t>
         </is>
       </c>
-      <c r="B24" s="70" t="inlineStr">
+      <c r="B24" s="72" t="inlineStr">
         <is>
           <t>Wellbeing→human escalation, safeguarding workflow, consent controls, PII redaction</t>
         </is>
@@ -9294,12 +9307,12 @@
       <c r="F24" s="46" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="41">
-      <c r="A25" s="67" t="inlineStr">
+      <c r="A25" s="69" t="inlineStr">
         <is>
           <t>2. AI quality &amp; cost monitoring</t>
         </is>
       </c>
-      <c r="B25" s="70" t="inlineStr">
+      <c r="B25" s="72" t="inlineStr">
         <is>
           <t>Latency / token / cost / version logging; grounding + hallucination measurement</t>
         </is>
@@ -9310,12 +9323,12 @@
       <c r="F25" s="46" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="41">
-      <c r="A26" s="67" t="inlineStr">
+      <c r="A26" s="69" t="inlineStr">
         <is>
           <t>3. Training-data pipeline</t>
         </is>
       </c>
-      <c r="B26" s="70" t="inlineStr">
+      <c r="B26" s="72" t="inlineStr">
         <is>
           <t>Interaction-logging schema, redaction, dataset versioning, model registry + rollback</t>
         </is>
@@ -9326,12 +9339,12 @@
       <c r="F26" s="46" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="41">
-      <c r="A27" s="67" t="inlineStr">
+      <c r="A27" s="69" t="inlineStr">
         <is>
           <t>4. Frontend wiring</t>
         </is>
       </c>
-      <c r="B27" s="70" t="inlineStr">
+      <c r="B27" s="72" t="inlineStr">
         <is>
           <t>Recommendation accept/complete widget, teacher AI-override UI, unified health card</t>
         </is>
@@ -9342,12 +9355,12 @@
       <c r="F27" s="46" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="41">
-      <c r="A28" s="67" t="inlineStr">
+      <c r="A28" s="69" t="inlineStr">
         <is>
           <t>5. Model + prompt version logging</t>
         </is>
       </c>
-      <c r="B28" s="70" t="inlineStr">
+      <c r="B28" s="72" t="inlineStr">
         <is>
           <t>Log which model / prompt / retrieval config produced each AI output (feeds quality + training-data work)</t>
         </is>
@@ -9393,452 +9406,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="41">
-      <c r="A1" s="78" t="inlineStr">
+      <c r="A1" s="80" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B1" s="78" t="inlineStr">
+      <c r="B1" s="80" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="C1" s="78" t="inlineStr">
+      <c r="C1" s="80" t="inlineStr">
         <is>
           <t>Current progress</t>
         </is>
       </c>
-      <c r="D1" s="78" t="inlineStr">
+      <c r="D1" s="80" t="inlineStr">
         <is>
           <t>Remaining gap</t>
         </is>
       </c>
-      <c r="E1" s="78" t="inlineStr">
+      <c r="E1" s="80" t="inlineStr">
         <is>
           <t>Acceptance check</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30.75" customHeight="1" s="41">
-      <c r="A2" s="79" t="n">
+      <c r="A2" s="81" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="79" t="inlineStr">
+      <c r="B2" s="81" t="inlineStr">
         <is>
           <t>ML Engine (weighted EMA mastery, at-risk detection, class trends)</t>
         </is>
       </c>
-      <c r="C2" s="79" t="inlineStr">
+      <c r="C2" s="81" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="D2" s="79" t="inlineStr">
+      <c r="D2" s="81" t="inlineStr">
         <is>
           <t>Event-stream EMA and attendance-aware risk bands are live; forecast accuracy still needs longitudinal validation.</t>
         </is>
       </c>
-      <c r="E2" s="79" t="inlineStr">
+      <c r="E2" s="81" t="inlineStr">
         <is>
           <t>Run against longitudinal fixture data and record accuracy/error metrics.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30.75" customHeight="1" s="41">
-      <c r="A3" s="79" t="n">
+      <c r="A3" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="79" t="inlineStr">
+      <c r="B3" s="81" t="inlineStr">
         <is>
           <t>AI-generated Learning Path (bridge from gap → target topic)</t>
         </is>
       </c>
-      <c r="C3" s="79" t="inlineStr">
+      <c r="C3" s="81" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="D3" s="79" t="inlineStr">
+      <c r="D3" s="81" t="inlineStr">
         <is>
           <t>Weekly plan generated from mastery + recs; AI bridge-path for an arbitrary gap→target still limited</t>
         </is>
       </c>
-      <c r="E3" s="79" t="inlineStr">
+      <c r="E3" s="81" t="inlineStr">
         <is>
           <t>Implement the gap, add a focused regression test, and verify the related API/UI flow.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1" s="41">
-      <c r="A4" s="79" t="n">
+      <c r="A4" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="79" t="inlineStr">
+      <c r="B4" s="81" t="inlineStr">
         <is>
           <t>Worksheet / Homework Generation (personalised to mastery gaps)</t>
         </is>
       </c>
-      <c r="C4" s="79" t="inlineStr">
+      <c r="C4" s="81" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D4" s="79" t="inlineStr">
+      <c r="D4" s="81" t="inlineStr">
         <is>
           <t>POST /api/ai-teacher/worksheet generates worksheets; not personalised to individual mastery gaps</t>
         </is>
       </c>
-      <c r="E4" s="79" t="inlineStr">
+      <c r="E4" s="81" t="inlineStr">
         <is>
           <t>Implement the gap, add a focused regression test, and verify the related API/UI flow.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30.75" customHeight="1" s="41">
-      <c r="A5" s="79" t="n">
+      <c r="A5" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="79" t="inlineStr">
+      <c r="B5" s="81" t="inlineStr">
         <is>
           <t>Adaptive Difficulty (adjust question hardness based on mastery)</t>
         </is>
       </c>
-      <c r="C5" s="79" t="inlineStr">
+      <c r="C5" s="81" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="D5" s="79" t="inlineStr">
+      <c r="D5" s="81" t="inlineStr">
         <is>
           <t>Mastery-derived Bloom band drives question difficulty; no full IRT/adaptive item selection</t>
         </is>
       </c>
-      <c r="E5" s="79" t="inlineStr">
+      <c r="E5" s="81" t="inlineStr">
         <is>
           <t>Implement the gap, add a focused regression test, and verify the related API/UI flow.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30.75" customHeight="1" s="41">
-      <c r="A6" s="79" t="n">
+      <c r="A6" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="79" t="inlineStr">
+      <c r="B6" s="81" t="inlineStr">
         <is>
           <t>AI Question Paper Generator (teacher selects topic + Bloom)</t>
         </is>
       </c>
-      <c r="C6" s="79" t="inlineStr">
+      <c r="C6" s="81" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="D6" s="79" t="inlineStr">
+      <c r="D6" s="81" t="inlineStr">
         <is>
           <t>Bloom-level question generation exists (bloom_question.txt); teacher UI for Bloom/difficulty selection pending</t>
         </is>
       </c>
-      <c r="E6" s="79" t="inlineStr">
+      <c r="E6" s="81" t="inlineStr">
         <is>
           <t>Expose the workflow in the relevant portal UI and add a user-flow test.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30.75" customHeight="1" s="41">
-      <c r="A7" s="79" t="n">
+      <c r="A7" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="79" t="inlineStr">
+      <c r="B7" s="81" t="inlineStr">
         <is>
           <t>Retention / Forgetting Model (knowledge decay over time)</t>
         </is>
       </c>
-      <c r="C7" s="79" t="inlineStr">
+      <c r="C7" s="81" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="D7" s="79" t="inlineStr">
+      <c r="D7" s="81" t="inlineStr">
         <is>
           <t>SM-2 schedules now expose an exponential retention estimate and fading/at-risk status through /api/spaced-repetition/retention; chart UI remains.</t>
         </is>
       </c>
-      <c r="E7" s="79" t="inlineStr">
+      <c r="E7" s="81" t="inlineStr">
         <is>
           <t>Expose the workflow in the relevant portal UI and add a user-flow test.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30.75" customHeight="1" s="41">
-      <c r="A8" s="79" t="n">
+      <c r="A8" s="81" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="79" t="inlineStr">
+      <c r="B8" s="81" t="inlineStr">
         <is>
           <t>Misconceptions Engine (explicit error model per topic/student)</t>
         </is>
       </c>
-      <c r="C8" s="79" t="inlineStr">
+      <c r="C8" s="81" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="D8" s="79" t="inlineStr">
+      <c r="D8" s="81" t="inlineStr">
         <is>
           <t>Class-wide misconception aggregation (classMisconceptions) + misconception tutor mode; per-student explicit misconception model pending</t>
         </is>
       </c>
-      <c r="E8" s="79" t="inlineStr">
+      <c r="E8" s="81" t="inlineStr">
         <is>
           <t>Implement the gap, add a focused regression test, and verify the related API/UI flow.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30.75" customHeight="1" s="41">
-      <c r="A9" s="79" t="n">
+      <c r="A9" s="81" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="79" t="inlineStr">
+      <c r="B9" s="81" t="inlineStr">
         <is>
           <t>Multidimensional Engagement (situational + behavioural + emotional)</t>
         </is>
       </c>
-      <c r="C9" s="79" t="inlineStr">
+      <c r="C9" s="81" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="D9" s="79" t="inlineStr">
+      <c r="D9" s="81" t="inlineStr">
         <is>
           <t>Behavioural, recency-based situational, and optional wellbeing-based emotional dimensions are available; dashboard presentation remains.</t>
         </is>
       </c>
-      <c r="E9" s="79" t="inlineStr">
+      <c r="E9" s="81" t="inlineStr">
         <is>
           <t>Expose the workflow in the relevant portal UI and add a user-flow test.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="41">
-      <c r="A10" s="79" t="n">
+      <c r="A10" s="81" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="79" t="inlineStr">
+      <c r="B10" s="81" t="inlineStr">
         <is>
           <t>Student Agency (learner control over learning path)</t>
         </is>
       </c>
-      <c r="C10" s="79" t="inlineStr">
+      <c r="C10" s="81" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="D10" s="79" t="inlineStr">
+      <c r="D10" s="81" t="inlineStr">
         <is>
           <t>Student can accept/dismiss/complete recommendations; no learning-path selection UI</t>
         </is>
       </c>
-      <c r="E10" s="79" t="inlineStr">
+      <c r="E10" s="81" t="inlineStr">
         <is>
           <t>Expose the workflow in the relevant portal UI and add a user-flow test.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30.75" customHeight="1" s="41">
-      <c r="A11" s="79" t="n">
+      <c r="A11" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="79" t="inlineStr">
+      <c r="B11" s="81" t="inlineStr">
         <is>
           <t>Explainable AI (why did AI recommend / answer this?)</t>
         </is>
       </c>
-      <c r="C11" s="79" t="inlineStr">
+      <c r="C11" s="81" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D11" s="79" t="inlineStr">
+      <c r="D11" s="81" t="inlineStr">
         <is>
           <t>Recommendations carry an explainability string; no reasoning-trace/lineage logging for tutor + evaluator</t>
         </is>
       </c>
-      <c r="E11" s="79" t="inlineStr">
+      <c r="E11" s="81" t="inlineStr">
         <is>
           <t>Implement the gap, add a focused regression test, and verify the related API/UI flow.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30.75" customHeight="1" s="41">
-      <c r="A12" s="79" t="n">
+      <c r="A12" s="81" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="79" t="inlineStr">
+      <c r="B12" s="81" t="inlineStr">
         <is>
           <t>Evidence Testing (prove platform improves learning outcomes)</t>
         </is>
       </c>
-      <c r="C12" s="79" t="inlineStr">
+      <c r="C12" s="81" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D12" s="79" t="inlineStr">
+      <c r="D12" s="81" t="inlineStr">
         <is>
           <t>Assessment-evidence summaries + daily regression forecast infra; no pre/post outcome-measurement framework, forecast unvalidated</t>
         </is>
       </c>
-      <c r="E12" s="79" t="inlineStr">
+      <c r="E12" s="81" t="inlineStr">
         <is>
           <t>Run against longitudinal fixture data and record accuracy/error metrics.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="41">
-      <c r="A13" s="79" t="n">
+      <c r="A13" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="79" t="inlineStr">
+      <c r="B13" s="81" t="inlineStr">
         <is>
           <t>AI / Data Ethics Framework (child-centered, beyond RBAC)</t>
         </is>
       </c>
-      <c r="C13" s="79" t="inlineStr">
+      <c r="C13" s="81" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="D13" s="79" t="inlineStr">
+      <c r="D13" s="81" t="inlineStr">
         <is>
           <t>JWT + RBAC + tenant isolation; no child-ethics/consent framework</t>
         </is>
       </c>
-      <c r="E13" s="79" t="inlineStr">
+      <c r="E13" s="81" t="inlineStr">
         <is>
           <t>Add the policy model/enforcement, audit event, and negative authorization tests.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30.75" customHeight="1" s="41">
-      <c r="A14" s="79" t="n">
+      <c r="A14" s="81" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="79" t="inlineStr">
+      <c r="B14" s="81" t="inlineStr">
         <is>
           <t>Image Understanding (student uploads photo of problem)</t>
         </is>
       </c>
-      <c r="C14" s="79" t="inlineStr">
+      <c r="C14" s="81" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D14" s="79" t="inlineStr">
+      <c r="D14" s="81" t="inlineStr">
         <is>
           <t>vision module: POST /vision/explain-image + PDF-page vision on ingest + visual_explain mode; student photo-of-problem upload flow pending</t>
         </is>
       </c>
-      <c r="E14" s="79" t="inlineStr">
+      <c r="E14" s="81" t="inlineStr">
         <is>
           <t>Implement the gap, add a focused regression test, and verify the related API/UI flow.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30.75" customHeight="1" s="41">
-      <c r="A15" s="79" t="n">
+      <c r="A15" s="81" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="79" t="inlineStr">
+      <c r="B15" s="81" t="inlineStr">
         <is>
           <t>Math Solver (step-by-step equation solving)</t>
         </is>
       </c>
-      <c r="C15" s="79" t="inlineStr">
+      <c r="C15" s="81" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="D15" s="79" t="inlineStr">
+      <c r="D15" s="81" t="inlineStr">
         <is>
           <t>stem module + stem/verifier.py math-answer verification; step-by-step solving UI + dedicated math model pending</t>
         </is>
       </c>
-      <c r="E15" s="79" t="inlineStr">
+      <c r="E15" s="81" t="inlineStr">
         <is>
           <t>Expose the workflow in the relevant portal UI and add a user-flow test.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="41">
-      <c r="A16" s="79" t="n">
+      <c r="A16" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="79" t="inlineStr">
+      <c r="B16" s="81" t="inlineStr">
         <is>
           <t>Topic Failure Prediction (predict fail before test happens)</t>
         </is>
       </c>
-      <c r="C16" s="79" t="inlineStr">
+      <c r="C16" s="81" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D16" s="79" t="inlineStr">
+      <c r="D16" s="81" t="inlineStr">
         <is>
           <t>learningEvidenceService.forecastScores infra; not validated, not surfaced</t>
         </is>
       </c>
-      <c r="E16" s="79" t="inlineStr">
+      <c r="E16" s="81" t="inlineStr">
         <is>
           <t>Expose the workflow in the relevant portal UI and add a user-flow test.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30.75" customHeight="1" s="41">
-      <c r="A17" s="79" t="n">
+      <c r="A17" s="81" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="79" t="inlineStr">
+      <c r="B17" s="81" t="inlineStr">
         <is>
           <t>Performance Forecasting (predicted score on next test)</t>
         </is>
       </c>
-      <c r="C17" s="79" t="inlineStr">
+      <c r="C17" s="81" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="D17" s="79" t="inlineStr">
+      <c r="D17" s="81" t="inlineStr">
         <is>
           <t>Daily least-squares score forecast (forecast-v1) + class forecast; accuracy not validated on longitudinal data</t>
         </is>
       </c>
-      <c r="E17" s="79" t="inlineStr">
+      <c r="E17" s="81" t="inlineStr">
         <is>
           <t>Run against longitudinal fixture data and record accuracy/error metrics.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30.75" customHeight="1" s="41">
-      <c r="A18" s="79" t="n">
+      <c r="A18" s="81" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="79" t="inlineStr">
+      <c r="B18" s="81" t="inlineStr">
         <is>
           <t>At-risk / Dropout Risk Prediction (ML model)</t>
         </is>
       </c>
-      <c r="C18" s="79" t="inlineStr">
+      <c r="C18" s="81" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D18" s="79" t="inlineStr">
+      <c r="D18" s="81" t="inlineStr">
         <is>
           <t>Attendance + mastery + trend risk factors and an interpretable dropout-risk band are live; a dedicated trained model still needs longitudinal validation.</t>
         </is>
       </c>
-      <c r="E18" s="79" t="inlineStr">
+      <c r="E18" s="81" t="inlineStr">
         <is>
           <t>Run against longitudinal fixture data and record accuracy/error metrics.</t>
         </is>
